--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -196,7 +196,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -346,13 +346,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -805,7 +798,7 @@
     <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="59">
   <si>
     <t>##var</t>
   </si>
@@ -52,6 +52,9 @@
     <t>emnity_cfg_id</t>
   </si>
   <si>
+    <t>faction_id</t>
+  </si>
+  <si>
     <t>move_style</t>
   </si>
   <si>
@@ -64,9 +67,15 @@
     <t>is_peace</t>
   </si>
   <si>
+    <t>peace_dialog_id</t>
+  </si>
+  <si>
     <t>defeat_drop_id</t>
   </si>
   <si>
+    <t>not_target</t>
+  </si>
+  <si>
     <t>always_h_mode</t>
   </si>
   <si>
@@ -113,6 +122,9 @@
   </si>
   <si>
     <t>敌对类型</t>
+  </si>
+  <si>
+    <t>阵营</t>
   </si>
   <si>
     <t xml:space="preserve">移动类型
@@ -135,6 +147,10 @@
     <t>击败掉落</t>
   </si>
   <si>
+    <t>非目标单位
+用于剧情npc等</t>
+  </si>
+  <si>
     <t>永远h</t>
   </si>
   <si>
@@ -169,6 +185,18 @@
   </si>
   <si>
     <t>描述2</t>
+  </si>
+  <si>
+    <t>initial_orc_big</t>
+  </si>
+  <si>
+    <t>初始精英</t>
+  </si>
+  <si>
+    <t>game_init_luca_injured</t>
+  </si>
+  <si>
+    <t>初始受伤npc</t>
   </si>
   <si>
     <t>hp</t>
@@ -802,7 +830,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -810,6 +838,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1124,19 +1155,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <dimension ref="A1:Q9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="12.125" customWidth="1"/>
     <col min="5" max="5" width="17.125" customWidth="1"/>
     <col min="6" max="6" width="17.625" customWidth="1"/>
-    <col min="7" max="7" width="13.875" customWidth="1"/>
-    <col min="9" max="9" width="14.25" customWidth="1"/>
-    <col min="10" max="10" width="12.625" customWidth="1"/>
-    <col min="11" max="11" width="14.5" customWidth="1"/>
+    <col min="7" max="8" width="13.875" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="10" max="10" width="14.25" customWidth="1"/>
+    <col min="11" max="11" width="20" customWidth="1"/>
+    <col min="12" max="13" width="14.5" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
+    <col min="15" max="15" width="17.625" customWidth="1"/>
+    <col min="17" max="17" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1158,10 +1194,10 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
@@ -1179,216 +1215,342 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="K2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" t="s">
-        <v>18</v>
-      </c>
       <c r="N2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>19</v>
+      </c>
+      <c r="O2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="N3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" ht="81" spans="1:14">
+        <v>23</v>
+      </c>
+      <c r="O3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" ht="81" spans="1:17">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>36</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P4" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="B5" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F5" s="1">
         <v>10000</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
         <v>1</v>
       </c>
-      <c r="I5" t="s">
-        <v>40</v>
-      </c>
       <c r="J5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5">
+        <v>45</v>
+      </c>
+      <c r="K5" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5">
         <v>1</v>
       </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="B6" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>38</v>
       </c>
       <c r="F6" s="1">
         <v>10001</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
         <v>1</v>
       </c>
-      <c r="I6" t="s">
-        <v>40</v>
-      </c>
       <c r="J6" t="s">
-        <v>41</v>
-      </c>
-      <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6">
+        <v>45</v>
+      </c>
+      <c r="K6" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6">
         <v>1</v>
       </c>
-      <c r="M6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6">
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="B7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="1">
+        <v>10001</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>52</v>
+      </c>
+      <c r="O9" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1417,44 +1579,44 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D4" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:4">

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -196,7 +196,7 @@
     <t>game_init_luca_injured</t>
   </si>
   <si>
-    <t>初始受伤npc</t>
+    <t>卢卡</t>
   </si>
   <si>
     <t>hp</t>

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="unit_npc" sheetId="1" r:id="rId1"/>
@@ -175,7 +175,7 @@
     <t>default</t>
   </si>
   <si>
-    <t>default_npc_attack</t>
+    <t>default_orc_attack</t>
   </si>
   <si>
     <t>initial_orc_02</t>

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -82,6 +82,9 @@
     <t>ignore_attract_level</t>
   </si>
   <si>
+    <t>unit_bottom_size</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -95,6 +98,9 @@
   </si>
   <si>
     <t>bool</t>
+  </si>
+  <si>
+    <t>float</t>
   </si>
   <si>
     <t>##group</t>
@@ -157,6 +163,9 @@
     <t>忽略吸引等级</t>
   </si>
   <si>
+    <t>底部size</t>
+  </si>
+  <si>
     <t>initial_orc_01</t>
   </si>
   <si>
@@ -203,9 +212,6 @@
   </si>
   <si>
     <t>move_speed</t>
-  </si>
-  <si>
-    <t>float</t>
   </si>
   <si>
     <t>生命</t>
@@ -1155,7 +1161,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -1172,7 +1178,7 @@
     <col min="17" max="17" width="14.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1224,179 +1230,191 @@
       <c r="Q1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:18">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="H2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="N2" t="s">
         <v>20</v>
       </c>
-      <c r="L2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" t="s">
-        <v>19</v>
-      </c>
       <c r="O2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q2" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:18">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q3" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="R3" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="4" ht="81" spans="1:17">
+    <row r="4" ht="81" spans="1:18">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Q4" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="R4" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:18">
       <c r="B5" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F5" s="1">
         <v>10000</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -1405,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
@@ -1422,25 +1440,28 @@
       <c r="Q5">
         <v>0</v>
       </c>
+      <c r="R5">
+        <v>0.5</v>
+      </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:18">
       <c r="B6" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F6" s="1">
         <v>10001</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -1449,10 +1470,10 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -1466,25 +1487,28 @@
       <c r="Q6">
         <v>0</v>
       </c>
+      <c r="R6">
+        <v>0.5</v>
+      </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:18">
       <c r="B7" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F7" s="1">
         <v>10001</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -1493,10 +1517,10 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -1510,24 +1534,27 @@
       <c r="Q7">
         <v>0</v>
       </c>
+      <c r="R7">
+        <v>0.5</v>
+      </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:18">
       <c r="A8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:18">
       <c r="B9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1539,19 +1566,22 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
       </c>
       <c r="P9" t="b">
         <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -1579,44 +1609,44 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="1"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:4">

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="unit_npc" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="69">
   <si>
     <t>##var</t>
   </si>
@@ -206,6 +206,30 @@
   </si>
   <si>
     <t>卢卡</t>
+  </si>
+  <si>
+    <t>qigai_default</t>
+  </si>
+  <si>
+    <t>乞丐</t>
+  </si>
+  <si>
+    <t>hunhun</t>
+  </si>
+  <si>
+    <t>混混</t>
+  </si>
+  <si>
+    <t>default_monster</t>
+  </si>
+  <si>
+    <t>slime_red</t>
+  </si>
+  <si>
+    <t>史莱姆</t>
+  </si>
+  <si>
+    <t>chongzhuang_slime</t>
   </si>
   <si>
     <t>hp</t>
@@ -1161,14 +1185,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="12.125" customWidth="1"/>
     <col min="5" max="5" width="17.125" customWidth="1"/>
     <col min="6" max="6" width="17.625" customWidth="1"/>
-    <col min="7" max="8" width="13.875" customWidth="1"/>
+    <col min="7" max="7" width="20.625" customWidth="1"/>
+    <col min="8" max="8" width="13.875" customWidth="1"/>
     <col min="9" max="9" width="12.375" customWidth="1"/>
     <col min="10" max="10" width="14.25" customWidth="1"/>
     <col min="11" max="11" width="20" customWidth="1"/>
@@ -1581,6 +1606,132 @@
         <v>0</v>
       </c>
       <c r="R9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="B11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="1">
+        <v>10000</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+      <c r="N11">
+        <v>1</v>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="B12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="1">
+        <v>10000</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
+        <v>48</v>
+      </c>
+      <c r="K12" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>1</v>
+      </c>
+      <c r="O12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" t="b">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="B13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" t="s">
+        <v>62</v>
+      </c>
+      <c r="F13" s="1">
+        <v>10000</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13" t="s">
+        <v>48</v>
+      </c>
+      <c r="K13" t="s">
+        <v>64</v>
+      </c>
+      <c r="L13" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13" t="b">
+        <v>0</v>
+      </c>
+      <c r="R13">
         <v>0.5</v>
       </c>
     </row>
@@ -1609,10 +1760,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1643,10 +1794,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:4">

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="73">
   <si>
     <t>##var</t>
   </si>
@@ -230,6 +230,18 @@
   </si>
   <si>
     <t>chongzhuang_slime</t>
+  </si>
+  <si>
+    <t>civil</t>
+  </si>
+  <si>
+    <t>市民</t>
+  </si>
+  <si>
+    <t>civil_sleeping</t>
+  </si>
+  <si>
+    <t>睡觉市民</t>
   </si>
   <si>
     <t>hp</t>
@@ -1185,7 +1197,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -1735,6 +1747,88 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="14" spans="1:18">
+      <c r="B14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="1">
+        <v>10000</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14" t="s">
+        <v>48</v>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+      <c r="N14">
+        <v>1</v>
+      </c>
+      <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="1">
+        <v>10000</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15" t="s">
+        <v>48</v>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" t="b">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1760,10 +1854,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1794,10 +1888,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:4">

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="74">
   <si>
     <t>##var</t>
   </si>
@@ -212,6 +212,9 @@
   </si>
   <si>
     <t>乞丐</t>
+  </si>
+  <si>
+    <t>qigai_01</t>
   </si>
   <si>
     <t>hunhun</t>
@@ -1643,6 +1646,9 @@
       <c r="L11" t="b">
         <v>1</v>
       </c>
+      <c r="M11" t="s">
+        <v>59</v>
+      </c>
       <c r="N11">
         <v>1</v>
       </c>
@@ -1661,19 +1667,19 @@
     </row>
     <row r="12" spans="1:18">
       <c r="B12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" t="s">
         <v>60</v>
-      </c>
-      <c r="E12" t="s">
-        <v>59</v>
       </c>
       <c r="F12" s="1">
         <v>10000</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1690,6 +1696,9 @@
       <c r="L12" t="b">
         <v>0</v>
       </c>
+      <c r="M12" t="s">
+        <v>59</v>
+      </c>
       <c r="N12">
         <v>1</v>
       </c>
@@ -1705,19 +1714,19 @@
     </row>
     <row r="13" spans="1:18">
       <c r="B13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C13" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" t="s">
         <v>63</v>
-      </c>
-      <c r="E13" t="s">
-        <v>62</v>
       </c>
       <c r="F13" s="1">
         <v>10000</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -1729,7 +1738,7 @@
         <v>48</v>
       </c>
       <c r="K13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
@@ -1749,13 +1758,13 @@
     </row>
     <row r="14" spans="1:18">
       <c r="B14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" t="s">
         <v>66</v>
-      </c>
-      <c r="E14" t="s">
-        <v>65</v>
       </c>
       <c r="F14" s="1">
         <v>10000</v>
@@ -1775,6 +1784,9 @@
       <c r="L14" t="b">
         <v>1</v>
       </c>
+      <c r="M14" t="s">
+        <v>59</v>
+      </c>
       <c r="N14">
         <v>1</v>
       </c>
@@ -1790,13 +1802,13 @@
     </row>
     <row r="15" spans="1:18">
       <c r="B15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" t="s">
         <v>68</v>
-      </c>
-      <c r="E15" t="s">
-        <v>67</v>
       </c>
       <c r="F15" s="1">
         <v>10000</v>
@@ -1815,6 +1827,9 @@
       </c>
       <c r="L15" t="b">
         <v>1</v>
+      </c>
+      <c r="M15" t="s">
+        <v>59</v>
       </c>
       <c r="N15">
         <v>1</v>
@@ -1854,10 +1869,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1888,10 +1903,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:4">

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17775" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="unit_npc" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="76">
   <si>
     <t>##var</t>
   </si>
@@ -247,10 +247,16 @@
     <t>睡觉市民</t>
   </si>
   <si>
+    <t>level</t>
+  </si>
+  <si>
     <t>hp</t>
   </si>
   <si>
     <t>move_speed</t>
+  </si>
+  <si>
+    <t>等级</t>
   </si>
   <si>
     <t>生命</t>
@@ -1854,14 +1860,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="2" max="2" width="18.75" customWidth="1"/>
-    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="2" max="3" width="18.75" customWidth="1"/>
+    <col min="4" max="4" width="10.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1874,8 +1880,11 @@
       <c r="D1" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
@@ -1886,16 +1895,19 @@
         <v>20</v>
       </c>
       <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B3" s="1"/>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>27</v>
       </c>
@@ -1903,65 +1915,83 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>74</v>
+      </c>
+      <c r="E4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>10000</v>
       </c>
       <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
         <v>100</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="B6" s="1">
         <v>10001</v>
       </c>
       <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
         <v>110</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5">
       <c r="B7" s="1">
         <v>10002</v>
       </c>
       <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
         <v>120</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5">
       <c r="B8" s="1">
         <v>10003</v>
       </c>
       <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
         <v>130</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:5">
       <c r="B9" s="1">
         <v>10004</v>
       </c>
       <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
         <v>140</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>2</v>
       </c>
     </row>

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775" activeTab="1"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="unit_npc" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="97">
   <si>
     <t>##var</t>
   </si>
@@ -83,6 +83,9 @@
   </si>
   <si>
     <t>unit_bottom_size</t>
+  </si>
+  <si>
+    <t>no_unsensored</t>
   </si>
   <si>
     <t>##type</t>
@@ -166,6 +169,9 @@
     <t>底部size</t>
   </si>
   <si>
+    <t>是否不可失去意识</t>
+  </si>
+  <si>
     <t>initial_orc_01</t>
   </si>
   <si>
@@ -184,7 +190,7 @@
     <t>default</t>
   </si>
   <si>
-    <t>default_orc_attack</t>
+    <t>default_normal_attack</t>
   </si>
   <si>
     <t>initial_orc_02</t>
@@ -247,6 +253,51 @@
     <t>睡觉市民</t>
   </si>
   <si>
+    <t>h_spirit_small_01</t>
+  </si>
+  <si>
+    <t>鬼</t>
+  </si>
+  <si>
+    <t>h_spirit_small</t>
+  </si>
+  <si>
+    <t>h_spirit</t>
+  </si>
+  <si>
+    <t>default_h_attack|h_spirit_killed</t>
+  </si>
+  <si>
+    <t>h_spirit_small_02</t>
+  </si>
+  <si>
+    <t>h_spirit_small_03</t>
+  </si>
+  <si>
+    <t>h_spirit_middle_01</t>
+  </si>
+  <si>
+    <t>h_spirit_middle</t>
+  </si>
+  <si>
+    <t>h_spirit_middle_02</t>
+  </si>
+  <si>
+    <t>h_spirit_middle_03</t>
+  </si>
+  <si>
+    <t>h_spirit_big_01</t>
+  </si>
+  <si>
+    <t>h_spirit_big</t>
+  </si>
+  <si>
+    <t>h_spirit_big_02</t>
+  </si>
+  <si>
+    <t>h_spirit_big_03</t>
+  </si>
+  <si>
     <t>level</t>
   </si>
   <si>
@@ -256,6 +307,12 @@
     <t>move_speed</t>
   </si>
   <si>
+    <t>base_atk</t>
+  </si>
+  <si>
+    <t>h_power</t>
+  </si>
+  <si>
     <t>等级</t>
   </si>
   <si>
@@ -263,6 +320,12 @@
   </si>
   <si>
     <t>移速</t>
+  </si>
+  <si>
+    <t>基础攻击</t>
+  </si>
+  <si>
+    <t>h能力</t>
   </si>
 </sst>
 </file>
@@ -1206,7 +1269,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:S28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -1222,9 +1285,11 @@
     <col min="14" max="14" width="22" customWidth="1"/>
     <col min="15" max="15" width="17.625" customWidth="1"/>
     <col min="17" max="17" width="14.875" customWidth="1"/>
+    <col min="18" max="18" width="10.75" customWidth="1"/>
+    <col min="19" max="19" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1279,188 +1344,200 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:18">
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="H2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="N2" t="s">
         <v>21</v>
       </c>
-      <c r="L2" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" t="s">
-        <v>20</v>
-      </c>
       <c r="O2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Q2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:19">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="H3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Q3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" ht="81" spans="1:18">
+        <v>26</v>
+      </c>
+      <c r="S3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" ht="81" spans="1:19">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
+        <v>43</v>
+      </c>
+      <c r="S4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="B5" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F5" s="1">
         <v>10000</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -1469,10 +1546,10 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
@@ -1489,25 +1566,28 @@
       <c r="R5">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:18">
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="B6" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F6" s="1">
         <v>10001</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H6" s="1">
         <v>0</v>
@@ -1516,10 +1596,10 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -1536,25 +1616,28 @@
       <c r="R6">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="7" spans="1:18">
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="B7" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F7" s="1">
         <v>10001</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H7" s="1">
         <v>0</v>
@@ -1563,10 +1646,10 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -1583,24 +1666,30 @@
       <c r="R7">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="8" spans="1:18">
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18">
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="B9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1612,13 +1701,13 @@
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
       </c>
       <c r="M9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O9" t="b">
         <v>1</v>
@@ -1629,22 +1718,25 @@
       <c r="R9">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="11" spans="1:18">
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="B11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F11" s="1">
         <v>10000</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="I11">
         <v>1</v>
@@ -1653,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N11">
         <v>1</v>
@@ -1670,22 +1762,25 @@
       <c r="R11">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="12" spans="1:18">
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="B12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F12" s="1">
         <v>10000</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1694,16 +1789,16 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -1717,22 +1812,25 @@
       <c r="R12">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="13" spans="1:18">
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="B13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F13" s="1">
         <v>10000</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -1741,10 +1839,10 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
@@ -1761,22 +1859,25 @@
       <c r="R13">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="14" spans="1:18">
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
       <c r="B14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F14" s="1">
         <v>10000</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1785,13 +1886,13 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -1805,22 +1906,25 @@
       <c r="R14">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="15" spans="1:18">
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
       <c r="B15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F15" s="1">
         <v>10000</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -1829,13 +1933,13 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
       </c>
       <c r="M15" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="N15">
         <v>1</v>
@@ -1848,6 +1952,432 @@
       </c>
       <c r="R15">
         <v>0.5</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19">
+      <c r="B18" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18">
+        <v>300</v>
+      </c>
+      <c r="G18" t="s">
+        <v>75</v>
+      </c>
+      <c r="H18">
+        <v>6</v>
+      </c>
+      <c r="I18">
+        <v>3</v>
+      </c>
+      <c r="J18" t="s">
+        <v>75</v>
+      </c>
+      <c r="K18" t="s">
+        <v>76</v>
+      </c>
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="P18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0.5</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="2:19">
+      <c r="B19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" t="s">
+        <v>73</v>
+      </c>
+      <c r="E19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19">
+        <v>301</v>
+      </c>
+      <c r="G19" t="s">
+        <v>75</v>
+      </c>
+      <c r="H19">
+        <v>6</v>
+      </c>
+      <c r="I19">
+        <v>3</v>
+      </c>
+      <c r="J19" t="s">
+        <v>75</v>
+      </c>
+      <c r="K19" t="s">
+        <v>76</v>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="P19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0.5</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" spans="2:19">
+      <c r="B20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20">
+        <v>302</v>
+      </c>
+      <c r="G20" t="s">
+        <v>75</v>
+      </c>
+      <c r="H20">
+        <v>6</v>
+      </c>
+      <c r="I20">
+        <v>3</v>
+      </c>
+      <c r="J20" t="s">
+        <v>75</v>
+      </c>
+      <c r="K20" t="s">
+        <v>76</v>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="P20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0.5</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19">
+      <c r="B22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E22" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22">
+        <v>400</v>
+      </c>
+      <c r="G22" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22">
+        <v>6</v>
+      </c>
+      <c r="I22">
+        <v>3</v>
+      </c>
+      <c r="J22" t="s">
+        <v>75</v>
+      </c>
+      <c r="K22" t="s">
+        <v>76</v>
+      </c>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="P22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>0.5</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:19">
+      <c r="B23" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" t="s">
+        <v>73</v>
+      </c>
+      <c r="E23" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23">
+        <v>401</v>
+      </c>
+      <c r="G23" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23">
+        <v>6</v>
+      </c>
+      <c r="I23">
+        <v>3</v>
+      </c>
+      <c r="J23" t="s">
+        <v>75</v>
+      </c>
+      <c r="K23" t="s">
+        <v>76</v>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="P23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0.5</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19">
+      <c r="B24" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" t="s">
+        <v>80</v>
+      </c>
+      <c r="F24">
+        <v>402</v>
+      </c>
+      <c r="G24" t="s">
+        <v>75</v>
+      </c>
+      <c r="H24">
+        <v>6</v>
+      </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
+      <c r="J24" t="s">
+        <v>75</v>
+      </c>
+      <c r="K24" t="s">
+        <v>76</v>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="P24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0.5</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19">
+      <c r="B26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" t="s">
+        <v>84</v>
+      </c>
+      <c r="F26">
+        <v>501</v>
+      </c>
+      <c r="G26" t="s">
+        <v>75</v>
+      </c>
+      <c r="H26">
+        <v>6</v>
+      </c>
+      <c r="I26">
+        <v>3</v>
+      </c>
+      <c r="J26" t="s">
+        <v>75</v>
+      </c>
+      <c r="K26" t="s">
+        <v>76</v>
+      </c>
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="P26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>0.5</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19">
+      <c r="B27" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" t="s">
+        <v>84</v>
+      </c>
+      <c r="F27">
+        <v>502</v>
+      </c>
+      <c r="G27" t="s">
+        <v>75</v>
+      </c>
+      <c r="H27">
+        <v>6</v>
+      </c>
+      <c r="I27">
+        <v>3</v>
+      </c>
+      <c r="J27" t="s">
+        <v>75</v>
+      </c>
+      <c r="K27" t="s">
+        <v>76</v>
+      </c>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="P27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>0.5</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19">
+      <c r="B28" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" t="s">
+        <v>73</v>
+      </c>
+      <c r="E28" t="s">
+        <v>84</v>
+      </c>
+      <c r="F28">
+        <v>503</v>
+      </c>
+      <c r="G28" t="s">
+        <v>75</v>
+      </c>
+      <c r="H28">
+        <v>6</v>
+      </c>
+      <c r="I28">
+        <v>3</v>
+      </c>
+      <c r="J28" t="s">
+        <v>75</v>
+      </c>
+      <c r="K28" t="s">
+        <v>76</v>
+      </c>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="P28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>0.5</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1860,14 +2390,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="3" width="18.75" customWidth="1"/>
-    <col min="4" max="4" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="12.5" customWidth="1"/>
+    <col min="5" max="5" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1875,56 +2406,74 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="D1" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="E1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+        <v>89</v>
+      </c>
+      <c r="F1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B3" s="1"/>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>94</v>
+      </c>
+      <c r="F4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>10000</v>
@@ -1938,8 +2487,11 @@
       <c r="E5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="B6" s="1">
         <v>10001</v>
       </c>
@@ -1952,8 +2504,11 @@
       <c r="E6">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="B7" s="1">
         <v>10002</v>
       </c>
@@ -1966,8 +2521,11 @@
       <c r="E7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="B8" s="1">
         <v>10003</v>
       </c>
@@ -1980,8 +2538,11 @@
       <c r="E8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="B9" s="1">
         <v>10004</v>
       </c>
@@ -1993,6 +2554,189 @@
       </c>
       <c r="E9">
         <v>2</v>
+      </c>
+      <c r="F9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="B11" s="1">
+        <v>300</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
+      </c>
+      <c r="F11">
+        <v>5</v>
+      </c>
+      <c r="G11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12" s="1">
+        <v>301</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>8</v>
+      </c>
+      <c r="G12">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13" s="1">
+        <v>302</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>100</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <v>12</v>
+      </c>
+      <c r="G13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="B15" s="1">
+        <v>400</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>100</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15">
+        <v>5</v>
+      </c>
+      <c r="G15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="B16" s="1">
+        <v>401</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>100</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>8</v>
+      </c>
+      <c r="G16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="1">
+        <v>402</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>100</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+      <c r="F17">
+        <v>12</v>
+      </c>
+      <c r="G17">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="1">
+        <v>500</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>100</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <v>5</v>
+      </c>
+      <c r="G19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7">
+      <c r="B20" s="1">
+        <v>501</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>100</v>
+      </c>
+      <c r="E20">
+        <v>2</v>
+      </c>
+      <c r="F20">
+        <v>8</v>
+      </c>
+      <c r="G20">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="1">
+        <v>502</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>100</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>12</v>
+      </c>
+      <c r="G21">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="unit_npc" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="105">
   <si>
     <t>##var</t>
   </si>
@@ -310,9 +310,21 @@
     <t>base_atk</t>
   </si>
   <si>
+    <t>physical_power</t>
+  </si>
+  <si>
     <t>h_power</t>
   </si>
   <si>
+    <t>base_blurt_amount</t>
+  </si>
+  <si>
+    <t>base_blurt_dmg</t>
+  </si>
+  <si>
+    <t>default_h_shield</t>
+  </si>
+  <si>
     <t>等级</t>
   </si>
   <si>
@@ -325,7 +337,19 @@
     <t>基础攻击</t>
   </si>
   <si>
+    <t>肉体能力</t>
+  </si>
+  <si>
     <t>h能力</t>
+  </si>
+  <si>
+    <t>基础射精量</t>
+  </si>
+  <si>
+    <t>基础射精伤害</t>
+  </si>
+  <si>
+    <t>h默认盾</t>
   </si>
 </sst>
 </file>
@@ -2390,15 +2414,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="3" width="18.75" customWidth="1"/>
     <col min="4" max="4" width="12.5" customWidth="1"/>
     <col min="5" max="5" width="14.125" customWidth="1"/>
+    <col min="8" max="8" width="11.625" customWidth="1"/>
+    <col min="9" max="9" width="13.875" customWidth="1"/>
+    <col min="10" max="10" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2420,8 +2447,20 @@
       <c r="G1" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="H1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I1" t="s">
+        <v>93</v>
+      </c>
+      <c r="J1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -2443,14 +2482,26 @@
       <c r="G2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B3" s="1"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -2458,22 +2509,34 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>100</v>
+      </c>
+      <c r="H4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I4" t="s">
+        <v>102</v>
+      </c>
+      <c r="J4" t="s">
+        <v>103</v>
+      </c>
+      <c r="K4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="1"/>
       <c r="B5" s="1">
         <v>10000</v>
@@ -2490,8 +2553,17 @@
       <c r="F5">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="G5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>5</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="B6" s="1">
         <v>10001</v>
       </c>
@@ -2507,8 +2579,17 @@
       <c r="F6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="I6">
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="B7" s="1">
         <v>10002</v>
       </c>
@@ -2524,8 +2605,17 @@
       <c r="F7">
         <v>5</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="I7">
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="B8" s="1">
         <v>10003</v>
       </c>
@@ -2541,8 +2631,20 @@
       <c r="F8">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="G8">
+        <v>10</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <v>6</v>
+      </c>
+      <c r="K8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="B9" s="1">
         <v>10004</v>
       </c>
@@ -2558,8 +2660,20 @@
       <c r="F9">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="I9">
+        <v>5</v>
+      </c>
+      <c r="J9">
+        <v>6</v>
+      </c>
+      <c r="K9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="B11" s="1">
         <v>300</v>
       </c>
@@ -2576,10 +2690,19 @@
         <v>5</v>
       </c>
       <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="I11">
+        <v>5</v>
+      </c>
+      <c r="J11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="B12" s="1">
         <v>301</v>
       </c>
@@ -2596,10 +2719,19 @@
         <v>8</v>
       </c>
       <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
         <v>14</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="I12">
+        <v>5</v>
+      </c>
+      <c r="J12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="B13" s="1">
         <v>302</v>
       </c>
@@ -2616,10 +2748,19 @@
         <v>12</v>
       </c>
       <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="I13">
+        <v>5</v>
+      </c>
+      <c r="J13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="B15" s="1">
         <v>400</v>
       </c>
@@ -2636,10 +2777,19 @@
         <v>5</v>
       </c>
       <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="I15">
+        <v>5</v>
+      </c>
+      <c r="J15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="B16" s="1">
         <v>401</v>
       </c>
@@ -2656,10 +2806,19 @@
         <v>8</v>
       </c>
       <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="2:7">
+      <c r="I16">
+        <v>5</v>
+      </c>
+      <c r="J16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10">
       <c r="B17" s="1">
         <v>402</v>
       </c>
@@ -2676,10 +2835,19 @@
         <v>12</v>
       </c>
       <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="2:7">
+      <c r="I17">
+        <v>5</v>
+      </c>
+      <c r="J17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10">
       <c r="B19" s="1">
         <v>500</v>
       </c>
@@ -2696,10 +2864,19 @@
         <v>5</v>
       </c>
       <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="2:7">
+      <c r="I19">
+        <v>5</v>
+      </c>
+      <c r="J19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
       <c r="B20" s="1">
         <v>501</v>
       </c>
@@ -2716,10 +2893,19 @@
         <v>8</v>
       </c>
       <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20">
         <v>14</v>
       </c>
-    </row>
-    <row r="21" spans="2:7">
+      <c r="I20">
+        <v>5</v>
+      </c>
+      <c r="J20">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10">
       <c r="B21" s="1">
         <v>502</v>
       </c>
@@ -2736,7 +2922,16 @@
         <v>12</v>
       </c>
       <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
         <v>18</v>
+      </c>
+      <c r="I21">
+        <v>5</v>
+      </c>
+      <c r="J21">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -1828,7 +1828,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -1881,7 +1881,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -1931,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="T13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -1981,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -2031,7 +2031,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:21">

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="110">
   <si>
     <t>##var</t>
   </si>
@@ -257,6 +257,15 @@
   </si>
   <si>
     <t>睡觉市民</t>
+  </si>
+  <si>
+    <t>default_guard_01</t>
+  </si>
+  <si>
+    <t>守卫1</t>
+  </si>
+  <si>
+    <t>default_guard</t>
   </si>
   <si>
     <t>h_spirit_small_01</t>
@@ -1294,7 +1303,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U28"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="24" style="1" customWidth="1"/>
@@ -2034,74 +2043,85 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="2:21">
-      <c r="B18" t="s">
+    <row r="16" spans="1:21">
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16"/>
+      <c r="R16"/>
+      <c r="S16"/>
+    </row>
+    <row r="17" spans="2:21">
+      <c r="B17" t="s">
         <v>74</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C17" t="s">
         <v>75</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17">
+        <v>10000</v>
+      </c>
+      <c r="G17" t="s">
         <v>76</v>
       </c>
-      <c r="F18">
-        <v>300</v>
-      </c>
-      <c r="G18" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18">
-        <v>6</v>
-      </c>
-      <c r="I18">
-        <v>3</v>
-      </c>
-      <c r="J18" t="s">
-        <v>77</v>
-      </c>
-      <c r="K18" t="s">
-        <v>78</v>
-      </c>
-      <c r="L18" t="b">
-        <v>0</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
-      <c r="P18" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q18">
-        <v>0</v>
-      </c>
-      <c r="R18">
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17" t="s">
+        <v>52</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+      <c r="M17"/>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17" t="b">
+        <v>0</v>
+      </c>
+      <c r="R17">
         <v>0.5</v>
       </c>
-      <c r="S18" t="b">
-        <v>1</v>
-      </c>
-      <c r="T18" t="b">
-        <v>0</v>
-      </c>
-      <c r="U18" t="b">
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:21">
       <c r="B19" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" t="s">
         <v>79</v>
       </c>
-      <c r="C19" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" t="s">
-        <v>76</v>
-      </c>
       <c r="F19">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="G19" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H19">
         <v>6</v>
@@ -2110,10 +2130,10 @@
         <v>3</v>
       </c>
       <c r="J19" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K19" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -2142,19 +2162,19 @@
     </row>
     <row r="20" spans="2:21">
       <c r="B20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20">
+        <v>301</v>
+      </c>
+      <c r="G20" t="s">
         <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>75</v>
-      </c>
-      <c r="E20" t="s">
-        <v>76</v>
-      </c>
-      <c r="F20">
-        <v>302</v>
-      </c>
-      <c r="G20" t="s">
-        <v>77</v>
       </c>
       <c r="H20">
         <v>6</v>
@@ -2163,10 +2183,10 @@
         <v>3</v>
       </c>
       <c r="J20" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K20" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -2193,74 +2213,74 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:21">
-      <c r="B22" t="s">
+    <row r="21" spans="2:21">
+      <c r="B21" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21">
+        <v>302</v>
+      </c>
+      <c r="G21" t="s">
+        <v>80</v>
+      </c>
+      <c r="H21">
+        <v>6</v>
+      </c>
+      <c r="I21">
+        <v>3</v>
+      </c>
+      <c r="J21" t="s">
+        <v>80</v>
+      </c>
+      <c r="K21" t="s">
         <v>81</v>
       </c>
-      <c r="C22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22" t="s">
-        <v>82</v>
-      </c>
-      <c r="F22">
-        <v>400</v>
-      </c>
-      <c r="G22" t="s">
-        <v>77</v>
-      </c>
-      <c r="H22">
-        <v>6</v>
-      </c>
-      <c r="I22">
-        <v>3</v>
-      </c>
-      <c r="J22" t="s">
-        <v>77</v>
-      </c>
-      <c r="K22" t="s">
-        <v>78</v>
-      </c>
-      <c r="L22" t="b">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="P22" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="P21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
         <v>0.5</v>
       </c>
-      <c r="S22" t="b">
-        <v>1</v>
-      </c>
-      <c r="T22" t="b">
-        <v>0</v>
-      </c>
-      <c r="U22" t="b">
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U21" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="2:21">
       <c r="B23" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E23" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F23">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="G23" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H23">
         <v>6</v>
@@ -2269,10 +2289,10 @@
         <v>3</v>
       </c>
       <c r="J23" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K23" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -2301,19 +2321,19 @@
     </row>
     <row r="24" spans="2:21">
       <c r="B24" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E24" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="F24">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G24" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H24">
         <v>6</v>
@@ -2322,10 +2342,10 @@
         <v>3</v>
       </c>
       <c r="J24" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K24" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
@@ -2352,74 +2372,74 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="2:21">
-      <c r="B26" t="s">
+    <row r="25" spans="2:21">
+      <c r="B25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" t="s">
         <v>85</v>
       </c>
-      <c r="C26" t="s">
-        <v>75</v>
-      </c>
-      <c r="E26" t="s">
-        <v>86</v>
-      </c>
-      <c r="F26">
-        <v>501</v>
-      </c>
-      <c r="G26" t="s">
-        <v>77</v>
-      </c>
-      <c r="H26">
+      <c r="F25">
+        <v>402</v>
+      </c>
+      <c r="G25" t="s">
+        <v>80</v>
+      </c>
+      <c r="H25">
         <v>6</v>
       </c>
-      <c r="I26">
+      <c r="I25">
         <v>3</v>
       </c>
-      <c r="J26" t="s">
-        <v>77</v>
-      </c>
-      <c r="K26" t="s">
-        <v>78</v>
-      </c>
-      <c r="L26" t="b">
-        <v>0</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="P26" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q26">
-        <v>0</v>
-      </c>
-      <c r="R26">
+      <c r="J25" t="s">
+        <v>80</v>
+      </c>
+      <c r="K25" t="s">
+        <v>81</v>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="P25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
         <v>0.5</v>
       </c>
-      <c r="S26" t="b">
-        <v>1</v>
-      </c>
-      <c r="T26" t="b">
-        <v>0</v>
-      </c>
-      <c r="U26" t="b">
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="b">
+        <v>0</v>
+      </c>
+      <c r="U25" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="2:21">
       <c r="B27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E27" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F27">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G27" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H27">
         <v>6</v>
@@ -2428,10 +2448,10 @@
         <v>3</v>
       </c>
       <c r="J27" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K27" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
@@ -2460,19 +2480,19 @@
     </row>
     <row r="28" spans="2:21">
       <c r="B28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C28" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E28" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F28">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G28" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H28">
         <v>6</v>
@@ -2481,10 +2501,10 @@
         <v>3</v>
       </c>
       <c r="J28" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K28" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
@@ -2508,6 +2528,59 @@
         <v>0</v>
       </c>
       <c r="U28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:21">
+      <c r="B29" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" t="s">
+        <v>78</v>
+      </c>
+      <c r="E29" t="s">
+        <v>89</v>
+      </c>
+      <c r="F29">
+        <v>503</v>
+      </c>
+      <c r="G29" t="s">
+        <v>80</v>
+      </c>
+      <c r="H29">
+        <v>6</v>
+      </c>
+      <c r="I29">
+        <v>3</v>
+      </c>
+      <c r="J29" t="s">
+        <v>80</v>
+      </c>
+      <c r="K29" t="s">
+        <v>81</v>
+      </c>
+      <c r="L29" t="b">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="P29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>0.5</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="b">
+        <v>0</v>
+      </c>
+      <c r="U29" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2540,31 +2613,31 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="G1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="H1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="I1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="K1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -2616,31 +2689,31 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="G4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="I4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:11">

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="unit_npc" sheetId="1" r:id="rId1"/>
     <sheet name="unit_npc_attribute" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="desire_density_info" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="140">
   <si>
     <t>##var</t>
   </si>
@@ -76,6 +76,9 @@
     <t>defeat_drop_id</t>
   </si>
   <si>
+    <t>desire_density_type</t>
+  </si>
+  <si>
     <t>not_target</t>
   </si>
   <si>
@@ -106,6 +109,12 @@
     <t>vision_fov_deg</t>
   </si>
   <si>
+    <t>mind_tag</t>
+  </si>
+  <si>
+    <t>fallback_drop_id</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -119,6 +128,9 @@
   </si>
   <si>
     <t>bool</t>
+  </si>
+  <si>
+    <t>EDesireDensityType</t>
   </si>
   <si>
     <t>float</t>
@@ -177,6 +189,9 @@
     <t>击败掉落</t>
   </si>
   <si>
+    <t>desire浓度类型</t>
+  </si>
+  <si>
     <t>非目标单位
 用于剧情npc等</t>
   </si>
@@ -223,6 +238,12 @@
     <t>default_normal_attack</t>
   </si>
   <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>orc_common</t>
+  </si>
+  <si>
     <t>initial_orc_02</t>
   </si>
   <si>
@@ -307,6 +328,9 @@
     <t>default_h_attack|h_spirit_immune</t>
   </si>
   <si>
+    <t>None</t>
+  </si>
+  <si>
     <t>h_spirit_small_02</t>
   </si>
   <si>
@@ -404,6 +428,33 @@
   </si>
   <si>
     <t>h默认盾</t>
+  </si>
+  <si>
+    <t>desire_type</t>
+  </si>
+  <si>
+    <t>min_density</t>
+  </si>
+  <si>
+    <t>max_density</t>
+  </si>
+  <si>
+    <t>distribute_mean</t>
+  </si>
+  <si>
+    <t>distribute_std_dev</t>
+  </si>
+  <si>
+    <t>hard_cap</t>
+  </si>
+  <si>
+    <t>desire类型</t>
+  </si>
+  <si>
+    <t>Elite</t>
+  </si>
+  <si>
+    <t>Boss</t>
   </si>
 </sst>
 </file>
@@ -1342,7 +1393,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Y31"/>
+  <dimension ref="A1:AB31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="24" style="1" customWidth="1"/>
@@ -1355,15 +1406,15 @@
     <col min="10" max="10" width="14.25" style="1" customWidth="1"/>
     <col min="11" max="11" width="20" style="1" customWidth="1"/>
     <col min="12" max="14" width="14.5" style="1" customWidth="1"/>
-    <col min="15" max="15" width="22" style="1" customWidth="1"/>
-    <col min="16" max="16" width="17.625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="14.875" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.75" style="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5" style="1" customWidth="1"/>
-    <col min="21" max="21" width="11.75" style="1" customWidth="1"/>
+    <col min="15" max="16" width="22" style="1" customWidth="1"/>
+    <col min="17" max="17" width="17.625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="14.875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" style="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5" style="1" customWidth="1"/>
+    <col min="22" max="22" width="11.75" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:28">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1439,251 +1490,287 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:25">
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:28">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" t="s">
         <v>29</v>
       </c>
-      <c r="M2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N2" t="s">
-        <v>26</v>
-      </c>
       <c r="O2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="P2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="Q2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="R2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="S2" t="s">
         <v>30</v>
       </c>
       <c r="T2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="V2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="W2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="X2" t="s">
         <v>30</v>
       </c>
       <c r="Y2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:28">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="M3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="O3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="P3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Q3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="R3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="S3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="T3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="U3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="V3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="W3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="X3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Y3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" ht="81" customHeight="1" spans="1:25">
+        <v>36</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" ht="81" customHeight="1" spans="1:28">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="L4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="M4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="O4" t="s">
-        <v>46</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>48</v>
+        <v>50</v>
+      </c>
+      <c r="P4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="R4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="S4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="T4" t="s">
-        <v>51</v>
-      </c>
-      <c r="U4" t="b">
-        <v>0</v>
-      </c>
-      <c r="V4" t="s">
-        <v>48</v>
+        <v>55</v>
+      </c>
+      <c r="U4" t="s">
+        <v>56</v>
+      </c>
+      <c r="V4" t="b">
+        <v>0</v>
       </c>
       <c r="W4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="X4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="Y4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25">
+        <v>58</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28">
       <c r="B5" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F5">
         <v>10000</v>
       </c>
       <c r="G5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1692,10 +1779,10 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K5" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="L5" t="b">
         <v>0</v>
@@ -1706,49 +1793,55 @@
       <c r="O5">
         <v>1</v>
       </c>
-      <c r="Q5" t="b">
-        <v>0</v>
-      </c>
-      <c r="R5">
+      <c r="P5" t="s">
+        <v>67</v>
+      </c>
+      <c r="R5" t="b">
         <v>0</v>
       </c>
       <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
         <v>0.5</v>
       </c>
-      <c r="T5" t="b">
-        <v>0</v>
-      </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
-      <c r="W5">
+      <c r="V5" t="b">
         <v>0</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y5">
         <v>-1</v>
       </c>
-    </row>
-    <row r="6" spans="1:25">
+      <c r="Z5">
+        <v>-1</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28">
       <c r="B6" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" t="s">
         <v>63</v>
-      </c>
-      <c r="D6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" t="s">
-        <v>58</v>
       </c>
       <c r="F6">
         <v>10001</v>
       </c>
       <c r="G6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1757,10 +1850,10 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K6" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="L6" t="b">
         <v>0</v>
@@ -1771,49 +1864,52 @@
       <c r="O6">
         <v>1</v>
       </c>
-      <c r="Q6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R6">
+      <c r="P6" t="s">
+        <v>67</v>
+      </c>
+      <c r="R6" t="b">
         <v>0</v>
       </c>
       <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
         <v>0.5</v>
       </c>
-      <c r="T6" t="b">
-        <v>0</v>
-      </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
-      <c r="W6">
+      <c r="V6" t="b">
         <v>0</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y6">
         <v>-1</v>
       </c>
-    </row>
-    <row r="7" spans="1:25">
+      <c r="Z6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28">
       <c r="B7" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="E7" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F7">
         <v>10001</v>
       </c>
       <c r="G7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1822,10 +1918,10 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -1836,122 +1932,132 @@
       <c r="O7">
         <v>1</v>
       </c>
-      <c r="Q7" t="b">
-        <v>0</v>
-      </c>
-      <c r="R7">
+      <c r="P7" t="s">
+        <v>67</v>
+      </c>
+      <c r="R7" t="b">
         <v>0</v>
       </c>
       <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
         <v>0.5</v>
       </c>
-      <c r="T7" t="b">
-        <v>0</v>
-      </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
-      <c r="W7">
+      <c r="V7" t="b">
         <v>0</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y7">
         <v>-1</v>
       </c>
-    </row>
-    <row r="8" spans="1:25">
+      <c r="Z7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
-      <c r="T8" t="b">
-        <v>0</v>
-      </c>
-      <c r="W8">
+      <c r="P8"/>
+      <c r="U8" t="b">
         <v>0</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y8">
         <v>-1</v>
       </c>
-    </row>
-    <row r="9" spans="1:25">
+      <c r="Z8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28">
       <c r="B9" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>65</v>
+      </c>
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+      <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>74</v>
+      </c>
+      <c r="P9" t="s">
         <v>67</v>
       </c>
-      <c r="C9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9" t="s">
-        <v>60</v>
-      </c>
-      <c r="L9" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>67</v>
-      </c>
-      <c r="P9" t="b">
-        <v>1</v>
-      </c>
       <c r="Q9" t="b">
-        <v>0</v>
-      </c>
-      <c r="S9">
+        <v>1</v>
+      </c>
+      <c r="R9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9">
         <v>0.5</v>
       </c>
-      <c r="T9" t="b">
-        <v>0</v>
-      </c>
       <c r="U9" t="b">
         <v>0</v>
       </c>
-      <c r="W9">
+      <c r="V9" t="b">
         <v>0</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y9">
         <v>-1</v>
       </c>
-    </row>
-    <row r="11" spans="1:25">
+      <c r="Z9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28">
+      <c r="P10"/>
+    </row>
+    <row r="11" spans="1:28">
       <c r="B11" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F11">
         <v>10000</v>
       </c>
       <c r="G11" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I11">
         <v>1</v>
@@ -1963,54 +2069,57 @@
         <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="O11">
         <v>1</v>
       </c>
-      <c r="P11" t="b">
-        <v>0</v>
+      <c r="P11" t="s">
+        <v>67</v>
       </c>
       <c r="Q11" t="b">
         <v>0</v>
       </c>
-      <c r="R11">
-        <v>1</v>
+      <c r="R11" t="b">
+        <v>0</v>
       </c>
       <c r="S11">
+        <v>1</v>
+      </c>
+      <c r="T11">
         <v>0.5</v>
       </c>
-      <c r="T11" t="b">
-        <v>0</v>
-      </c>
       <c r="U11" t="b">
-        <v>1</v>
-      </c>
-      <c r="W11">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V11" t="b">
+        <v>1</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y11">
         <v>-1</v>
       </c>
-    </row>
-    <row r="12" spans="1:25">
+      <c r="Z11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:28">
       <c r="B12" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F12">
         <v>10000</v>
       </c>
       <c r="G12" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -2019,10 +2128,10 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K12" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="L12" t="b">
         <v>0</v>
@@ -2031,51 +2140,54 @@
         <v>0</v>
       </c>
       <c r="N12" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="O12">
         <v>1</v>
       </c>
-      <c r="P12" t="b">
-        <v>0</v>
+      <c r="P12" t="s">
+        <v>67</v>
       </c>
       <c r="Q12" t="b">
-        <v>1</v>
-      </c>
-      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="R12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12">
         <v>0.5</v>
       </c>
-      <c r="T12" t="b">
-        <v>0</v>
-      </c>
       <c r="U12" t="b">
-        <v>1</v>
-      </c>
-      <c r="W12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V12" t="b">
+        <v>1</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y12">
         <v>-1</v>
       </c>
-    </row>
-    <row r="13" spans="1:25">
+      <c r="Z12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28">
       <c r="B13" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E13" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F13">
         <v>10000</v>
       </c>
       <c r="G13" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -2084,10 +2196,10 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K13" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="L13" t="b">
         <v>0</v>
@@ -2098,46 +2210,49 @@
       <c r="O13">
         <v>1</v>
       </c>
-      <c r="P13" t="b">
-        <v>0</v>
+      <c r="P13" t="s">
+        <v>67</v>
       </c>
       <c r="Q13" t="b">
         <v>0</v>
       </c>
-      <c r="S13">
+      <c r="R13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13">
         <v>0.5</v>
       </c>
-      <c r="T13" t="b">
-        <v>0</v>
-      </c>
       <c r="U13" t="b">
-        <v>1</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V13" t="b">
+        <v>1</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y13">
         <v>-1</v>
       </c>
-    </row>
-    <row r="14" spans="1:25">
+      <c r="Z13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28">
       <c r="B14" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="E14" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F14">
         <v>10000</v>
       </c>
       <c r="G14" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2146,7 +2261,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
@@ -2155,51 +2270,54 @@
         <v>0</v>
       </c>
       <c r="N14" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="O14">
         <v>1</v>
       </c>
-      <c r="P14" t="b">
-        <v>0</v>
+      <c r="P14" t="s">
+        <v>67</v>
       </c>
       <c r="Q14" t="b">
         <v>0</v>
       </c>
-      <c r="S14">
+      <c r="R14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14">
         <v>0.5</v>
       </c>
-      <c r="T14" t="b">
-        <v>0</v>
-      </c>
       <c r="U14" t="b">
-        <v>1</v>
-      </c>
-      <c r="W14">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V14" t="b">
+        <v>1</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y14">
         <v>-1</v>
       </c>
-    </row>
-    <row r="15" spans="1:25">
+      <c r="Z14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28">
       <c r="B15" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="E15" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F15">
         <v>10000</v>
       </c>
       <c r="G15" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -2208,7 +2326,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
@@ -2217,37 +2335,40 @@
         <v>0</v>
       </c>
       <c r="N15" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="O15">
         <v>1</v>
       </c>
-      <c r="P15" t="b">
-        <v>0</v>
+      <c r="P15" t="s">
+        <v>67</v>
       </c>
       <c r="Q15" t="b">
         <v>0</v>
       </c>
-      <c r="S15">
+      <c r="R15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15">
         <v>0.5</v>
       </c>
-      <c r="T15" t="b">
-        <v>0</v>
-      </c>
       <c r="U15" t="b">
-        <v>1</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V15" t="b">
+        <v>1</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y15">
         <v>-1</v>
       </c>
-    </row>
-    <row r="16" spans="1:25">
+      <c r="Z15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28">
       <c r="B16"/>
       <c r="C16"/>
       <c r="E16"/>
@@ -2261,24 +2382,25 @@
       <c r="N16"/>
       <c r="O16"/>
       <c r="P16"/>
-      <c r="S16"/>
+      <c r="Q16"/>
       <c r="T16"/>
-    </row>
-    <row r="17" spans="2:25">
+      <c r="U16"/>
+    </row>
+    <row r="17" spans="2:26">
       <c r="B17" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="E17" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F17">
         <v>10000</v>
       </c>
       <c r="G17" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -2287,7 +2409,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
@@ -2299,46 +2421,52 @@
       <c r="O17">
         <v>1</v>
       </c>
-      <c r="P17" t="b">
-        <v>0</v>
+      <c r="P17" t="s">
+        <v>67</v>
       </c>
       <c r="Q17" t="b">
         <v>0</v>
       </c>
-      <c r="S17">
+      <c r="R17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17">
         <v>0.5</v>
       </c>
-      <c r="T17" t="b">
-        <v>0</v>
-      </c>
       <c r="U17" t="b">
-        <v>1</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="V17" t="b">
+        <v>1</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y17">
         <v>-1</v>
       </c>
-    </row>
-    <row r="19" spans="2:25">
+      <c r="Z17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:26">
+      <c r="P18"/>
+    </row>
+    <row r="19" spans="2:26">
       <c r="B19" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E19" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="F19">
         <v>300</v>
       </c>
       <c r="G19" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H19">
         <v>6</v>
@@ -2347,10 +2475,10 @@
         <v>3</v>
       </c>
       <c r="J19" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K19" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L19" t="b">
         <v>0</v>
@@ -2361,49 +2489,52 @@
       <c r="O19">
         <v>0</v>
       </c>
-      <c r="Q19" t="b">
-        <v>1</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
+      <c r="P19" t="s">
+        <v>97</v>
+      </c>
+      <c r="R19" t="b">
+        <v>1</v>
       </c>
       <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
         <v>0.5</v>
       </c>
-      <c r="T19" t="b">
-        <v>1</v>
-      </c>
       <c r="U19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="b">
-        <v>1</v>
-      </c>
-      <c r="W19">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="W19" t="b">
+        <v>1</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y19">
         <v>-1</v>
       </c>
-    </row>
-    <row r="20" spans="2:25">
+      <c r="Z19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:26">
       <c r="B20" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C20" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E20" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="F20">
         <v>301</v>
       </c>
       <c r="G20" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H20">
         <v>6</v>
@@ -2412,10 +2543,10 @@
         <v>3</v>
       </c>
       <c r="J20" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K20" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L20" t="b">
         <v>0</v>
@@ -2426,49 +2557,52 @@
       <c r="O20">
         <v>0</v>
       </c>
-      <c r="Q20" t="b">
-        <v>1</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
+      <c r="P20" t="s">
+        <v>97</v>
+      </c>
+      <c r="R20" t="b">
+        <v>1</v>
       </c>
       <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
         <v>0.5</v>
       </c>
-      <c r="T20" t="b">
-        <v>1</v>
-      </c>
       <c r="U20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" t="b">
-        <v>1</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="W20" t="b">
+        <v>1</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y20">
         <v>-1</v>
       </c>
-    </row>
-    <row r="21" spans="2:25">
+      <c r="Z20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:26">
       <c r="B21" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E21" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="F21">
         <v>302</v>
       </c>
       <c r="G21" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H21">
         <v>6</v>
@@ -2477,10 +2611,10 @@
         <v>3</v>
       </c>
       <c r="J21" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K21" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L21" t="b">
         <v>0</v>
@@ -2491,49 +2625,55 @@
       <c r="O21">
         <v>0</v>
       </c>
-      <c r="Q21" t="b">
-        <v>1</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
+      <c r="P21" t="s">
+        <v>97</v>
+      </c>
+      <c r="R21" t="b">
+        <v>1</v>
       </c>
       <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
         <v>0.5</v>
       </c>
-      <c r="T21" t="b">
-        <v>1</v>
-      </c>
       <c r="U21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" t="b">
-        <v>1</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="W21" t="b">
+        <v>1</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y21">
         <v>-1</v>
       </c>
-    </row>
-    <row r="23" spans="2:25">
+      <c r="Z21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:26">
+      <c r="P22"/>
+    </row>
+    <row r="23" spans="2:26">
       <c r="B23" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C23" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E23" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F23">
         <v>400</v>
       </c>
       <c r="G23" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H23">
         <v>6</v>
@@ -2542,10 +2682,10 @@
         <v>3</v>
       </c>
       <c r="J23" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K23" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L23" t="b">
         <v>0</v>
@@ -2556,49 +2696,52 @@
       <c r="O23">
         <v>0</v>
       </c>
-      <c r="Q23" t="b">
-        <v>1</v>
-      </c>
-      <c r="R23">
-        <v>0</v>
+      <c r="P23" t="s">
+        <v>97</v>
+      </c>
+      <c r="R23" t="b">
+        <v>1</v>
       </c>
       <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
         <v>0.5</v>
       </c>
-      <c r="T23" t="b">
-        <v>1</v>
-      </c>
       <c r="U23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V23" t="b">
-        <v>1</v>
-      </c>
-      <c r="W23">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="W23" t="b">
+        <v>1</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y23">
         <v>-1</v>
       </c>
-    </row>
-    <row r="24" spans="2:25">
+      <c r="Z23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:26">
       <c r="B24" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E24" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F24">
         <v>401</v>
       </c>
       <c r="G24" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H24">
         <v>6</v>
@@ -2607,10 +2750,10 @@
         <v>3</v>
       </c>
       <c r="J24" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K24" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L24" t="b">
         <v>0</v>
@@ -2621,49 +2764,52 @@
       <c r="O24">
         <v>0</v>
       </c>
-      <c r="Q24" t="b">
-        <v>1</v>
-      </c>
-      <c r="R24">
-        <v>0</v>
+      <c r="P24" t="s">
+        <v>97</v>
+      </c>
+      <c r="R24" t="b">
+        <v>1</v>
       </c>
       <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
         <v>0.5</v>
       </c>
-      <c r="T24" t="b">
-        <v>1</v>
-      </c>
       <c r="U24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V24" t="b">
-        <v>1</v>
-      </c>
-      <c r="W24">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="W24" t="b">
+        <v>1</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y24">
         <v>-1</v>
       </c>
-    </row>
-    <row r="25" spans="2:25">
+      <c r="Z24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:26">
       <c r="B25" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E25" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="F25">
         <v>402</v>
       </c>
       <c r="G25" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H25">
         <v>6</v>
@@ -2672,10 +2818,10 @@
         <v>3</v>
       </c>
       <c r="J25" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K25" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L25" t="b">
         <v>0</v>
@@ -2686,49 +2832,55 @@
       <c r="O25">
         <v>0</v>
       </c>
-      <c r="Q25" t="b">
-        <v>1</v>
-      </c>
-      <c r="R25">
-        <v>0</v>
+      <c r="P25" t="s">
+        <v>97</v>
+      </c>
+      <c r="R25" t="b">
+        <v>1</v>
       </c>
       <c r="S25">
+        <v>0</v>
+      </c>
+      <c r="T25">
         <v>0.5</v>
       </c>
-      <c r="T25" t="b">
-        <v>1</v>
-      </c>
       <c r="U25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" t="b">
-        <v>1</v>
-      </c>
-      <c r="W25">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="W25" t="b">
+        <v>1</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y25">
         <v>-1</v>
       </c>
-    </row>
-    <row r="27" spans="2:25">
+      <c r="Z25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:26">
+      <c r="P26"/>
+    </row>
+    <row r="27" spans="2:26">
       <c r="B27" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="C27" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E27" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F27">
         <v>501</v>
       </c>
       <c r="G27" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H27">
         <v>6</v>
@@ -2737,10 +2889,10 @@
         <v>3</v>
       </c>
       <c r="J27" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K27" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L27" t="b">
         <v>0</v>
@@ -2751,49 +2903,52 @@
       <c r="O27">
         <v>0</v>
       </c>
-      <c r="Q27" t="b">
-        <v>1</v>
-      </c>
-      <c r="R27">
-        <v>0</v>
+      <c r="P27" t="s">
+        <v>97</v>
+      </c>
+      <c r="R27" t="b">
+        <v>1</v>
       </c>
       <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
         <v>0.5</v>
       </c>
-      <c r="T27" t="b">
-        <v>1</v>
-      </c>
       <c r="U27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" t="b">
-        <v>1</v>
-      </c>
-      <c r="W27">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="W27" t="b">
+        <v>1</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y27">
         <v>-1</v>
       </c>
-    </row>
-    <row r="28" spans="2:25">
+      <c r="Z27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:26">
       <c r="B28" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E28" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F28">
         <v>502</v>
       </c>
       <c r="G28" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H28">
         <v>6</v>
@@ -2802,10 +2957,10 @@
         <v>3</v>
       </c>
       <c r="J28" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K28" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L28" t="b">
         <v>0</v>
@@ -2816,49 +2971,52 @@
       <c r="O28">
         <v>0</v>
       </c>
-      <c r="Q28" t="b">
-        <v>1</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
+      <c r="P28" t="s">
+        <v>97</v>
+      </c>
+      <c r="R28" t="b">
+        <v>1</v>
       </c>
       <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28">
         <v>0.5</v>
       </c>
-      <c r="T28" t="b">
-        <v>1</v>
-      </c>
       <c r="U28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" t="b">
-        <v>1</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="W28" t="b">
+        <v>1</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y28">
         <v>-1</v>
       </c>
-    </row>
-    <row r="29" spans="2:25">
+      <c r="Z28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:26">
       <c r="B29" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C29" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E29" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F29">
         <v>503</v>
       </c>
       <c r="G29" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H29">
         <v>6</v>
@@ -2867,10 +3025,10 @@
         <v>3</v>
       </c>
       <c r="J29" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="K29" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L29" t="b">
         <v>0</v>
@@ -2881,49 +3039,55 @@
       <c r="O29">
         <v>0</v>
       </c>
-      <c r="Q29" t="b">
-        <v>1</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
+      <c r="P29" t="s">
+        <v>97</v>
+      </c>
+      <c r="R29" t="b">
+        <v>1</v>
       </c>
       <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="T29">
         <v>0.5</v>
       </c>
-      <c r="T29" t="b">
-        <v>1</v>
-      </c>
       <c r="U29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29" t="b">
-        <v>1</v>
-      </c>
-      <c r="W29">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="W29" t="b">
+        <v>1</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y29">
         <v>-1</v>
       </c>
-    </row>
-    <row r="31" spans="2:25">
+      <c r="Z29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:26">
+      <c r="P30"/>
+    </row>
+    <row r="31" spans="2:26">
       <c r="B31" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C31" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="E31" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F31">
         <v>10000</v>
       </c>
       <c r="G31" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -2932,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K31" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="L31" t="b">
         <v>1</v>
@@ -2943,13 +3107,37 @@
       <c r="M31" t="b">
         <v>1</v>
       </c>
-      <c r="W31">
-        <v>0</v>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31" t="s">
+        <v>97</v>
+      </c>
+      <c r="R31" t="b">
+        <v>1</v>
+      </c>
+      <c r="S31">
+        <v>0</v>
+      </c>
+      <c r="T31">
+        <v>0.5</v>
+      </c>
+      <c r="U31" t="b">
+        <v>1</v>
+      </c>
+      <c r="V31" t="b">
+        <v>0</v>
+      </c>
+      <c r="W31" t="b">
+        <v>1</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="Y31">
+        <v>-1</v>
+      </c>
+      <c r="Z31">
         <v>-1</v>
       </c>
     </row>
@@ -2982,107 +3170,107 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D1" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="E1" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="F1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G1" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="H1" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="I1" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="J1" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="K1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B3"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E4" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F4" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="G4" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="H4" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="I4" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="J4" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="K4" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3492,9 +3680,172 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
+  <cols>
+    <col min="2" max="2" width="15.625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3"/>
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="B5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6">
+        <v>5000</v>
+      </c>
+      <c r="D6">
+        <v>35000</v>
+      </c>
+      <c r="E6">
+        <v>20000</v>
+      </c>
+      <c r="F6">
+        <v>6000</v>
+      </c>
+      <c r="G6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="B7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7">
+        <v>15000</v>
+      </c>
+      <c r="D7">
+        <v>55000</v>
+      </c>
+      <c r="E7">
+        <v>35000</v>
+      </c>
+      <c r="F7">
+        <v>8000</v>
+      </c>
+      <c r="G7">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="B8" t="s">
+        <v>139</v>
+      </c>
+      <c r="C8">
+        <v>25000</v>
+      </c>
+      <c r="D8">
+        <v>80000</v>
+      </c>
+      <c r="E8">
+        <v>50000</v>
+      </c>
+      <c r="F8">
+        <v>12000</v>
+      </c>
+      <c r="G8">
+        <v>100000</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="2"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="unit_npc" sheetId="1" r:id="rId1"/>

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="143">
   <si>
     <t>##var</t>
   </si>
@@ -374,6 +374,15 @@
   </si>
   <si>
     <t>watcher_armor</t>
+  </si>
+  <si>
+    <t>summon_ally_turret_01</t>
+  </si>
+  <si>
+    <t>炮台</t>
+  </si>
+  <si>
+    <t>ally_turret</t>
   </si>
   <si>
     <t>level</t>
@@ -1393,7 +1402,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AB31"/>
+  <dimension ref="A1:AB33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="24" style="1" customWidth="1"/>
@@ -3138,6 +3147,72 @@
         <v>-1</v>
       </c>
       <c r="Z31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26">
+      <c r="B33" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C33" t="s">
+        <v>114</v>
+      </c>
+      <c r="E33" t="s">
+        <v>115</v>
+      </c>
+      <c r="F33">
+        <v>10000</v>
+      </c>
+      <c r="G33" t="s">
+        <v>64</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>1</v>
+      </c>
+      <c r="J33" t="s">
+        <v>65</v>
+      </c>
+      <c r="K33" t="s">
+        <v>66</v>
+      </c>
+      <c r="L33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33"/>
+      <c r="O33">
+        <v>1</v>
+      </c>
+      <c r="P33" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q33" t="b">
+        <v>0</v>
+      </c>
+      <c r="R33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33">
+        <v>0.5</v>
+      </c>
+      <c r="U33" t="b">
+        <v>0</v>
+      </c>
+      <c r="V33" t="b">
+        <v>1</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>-1</v>
+      </c>
+      <c r="Z33">
         <v>-1</v>
       </c>
     </row>
@@ -3170,31 +3245,31 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F1" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G1" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="H1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="I1" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="J1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -3246,31 +3321,31 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3692,22 +3767,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E1" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -3759,10 +3834,10 @@
         <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -3807,7 +3882,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="B7" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C7">
         <v>15000</v>
@@ -3827,7 +3902,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="B8" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C8">
         <v>25000</v>

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="155">
   <si>
     <t>##var</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>skill_list</t>
+  </si>
+  <si>
+    <t>h_behave_list</t>
   </si>
   <si>
     <t>is_peace</t>
@@ -192,6 +195,9 @@
     <t>技能列表</t>
   </si>
   <si>
+    <t>H技能列表</t>
+  </si>
+  <si>
     <t>是否和平</t>
   </si>
   <si>
@@ -248,6 +254,9 @@
   </si>
   <si>
     <t>default_normal_attack</t>
+  </si>
+  <si>
+    <t>default_h_attack|default_enemy_harass|default_enemy_knockdown_push</t>
   </si>
   <si>
     <t>Normal</t>
@@ -1429,7 +1438,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD34"/>
+  <dimension ref="A1:AE34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="24" style="1" customWidth="1"/>
@@ -1441,16 +1450,18 @@
     <col min="9" max="9" width="12.375" style="1" customWidth="1"/>
     <col min="10" max="10" width="14.25" style="1" customWidth="1"/>
     <col min="11" max="11" width="20" style="1" customWidth="1"/>
-    <col min="12" max="14" width="14.5" style="1" customWidth="1"/>
-    <col min="15" max="16" width="22" style="1" customWidth="1"/>
-    <col min="17" max="17" width="17.625" style="1" customWidth="1"/>
-    <col min="19" max="19" width="14.875" style="1" customWidth="1"/>
-    <col min="20" max="20" width="10.75" style="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5" style="1" customWidth="1"/>
-    <col min="22" max="22" width="11.75" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19" style="1" customWidth="1"/>
+    <col min="13" max="13" width="18.5" style="1" customWidth="1"/>
+    <col min="14" max="15" width="14.5" style="1" customWidth="1"/>
+    <col min="16" max="17" width="22" style="1" customWidth="1"/>
+    <col min="18" max="18" width="17.625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="14.875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="10.75" style="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5" style="1" customWidth="1"/>
+    <col min="23" max="23" width="11.75" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30">
+    <row r="1" spans="1:31">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1541,296 +1552,308 @@
       <c r="AD1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:30">
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" t="s">
         <v>32</v>
       </c>
-      <c r="G2" t="s">
-        <v>31</v>
-      </c>
       <c r="H2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" t="s">
+        <v>34</v>
+      </c>
+      <c r="K2" t="s">
         <v>32</v>
       </c>
-      <c r="I2" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K2" t="s">
-        <v>31</v>
-      </c>
       <c r="L2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M2" t="s">
         <v>35</v>
       </c>
       <c r="N2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="P2" t="s">
         <v>32</v>
       </c>
       <c r="Q2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" t="s">
+        <v>37</v>
+      </c>
+      <c r="S2" t="s">
         <v>36</v>
       </c>
-      <c r="R2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S2" t="s">
-        <v>35</v>
-      </c>
       <c r="T2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="U2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="V2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="W2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Z2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="AA2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AB2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="AC2" t="s">
         <v>32</v>
       </c>
       <c r="AD2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:30">
+        <v>33</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3" t="s">
         <v>40</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>40</v>
       </c>
-      <c r="F3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" t="s">
-        <v>39</v>
-      </c>
       <c r="H3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="T3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="V3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="W3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="X3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Z3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AA3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AB3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AC3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AD3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" ht="81" customHeight="1" spans="1:30">
+        <v>40</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" ht="81" customHeight="1" spans="1:31">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="M4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N4" t="s">
-        <v>53</v>
-      </c>
-      <c r="P4" t="s">
         <v>54</v>
       </c>
+      <c r="O4" t="s">
+        <v>55</v>
+      </c>
       <c r="Q4" t="s">
-        <v>55</v>
-      </c>
-      <c r="R4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="S4" t="s">
+      <c r="R4" t="s">
         <v>57</v>
       </c>
+      <c r="S4" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="T4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U4" t="s">
+        <v>60</v>
+      </c>
+      <c r="V4" t="s">
+        <v>61</v>
+      </c>
+      <c r="W4" t="s">
+        <v>62</v>
+      </c>
+      <c r="X4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="s">
         <v>59</v>
       </c>
-      <c r="V4" t="s">
-        <v>60</v>
-      </c>
-      <c r="W4" t="b">
-        <v>0</v>
-      </c>
-      <c r="X4" t="s">
-        <v>57</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>61</v>
-      </c>
       <c r="Z4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB4" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AC4" t="s">
         <v>28</v>
       </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30">
+      <c r="AD4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31">
       <c r="B5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F5">
         <v>10000</v>
       </c>
       <c r="G5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1839,75 +1862,78 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K5" t="s">
+        <v>71</v>
+      </c>
+      <c r="L5" t="s">
+        <v>72</v>
+      </c>
+      <c r="M5" t="s">
+        <v>73</v>
+      </c>
+      <c r="N5" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5" t="s">
+        <v>74</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0.5</v>
+      </c>
+      <c r="W5" t="b">
+        <v>0</v>
+      </c>
+      <c r="X5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>-1</v>
+      </c>
+      <c r="AB5">
+        <v>-1</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>75</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31">
+      <c r="B6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" t="s">
         <v>69</v>
-      </c>
-      <c r="L5" t="s">
-        <v>70</v>
-      </c>
-      <c r="M5" t="b">
-        <v>0</v>
-      </c>
-      <c r="N5" t="b">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>71</v>
-      </c>
-      <c r="S5" t="b">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0.5</v>
-      </c>
-      <c r="V5" t="b">
-        <v>0</v>
-      </c>
-      <c r="W5" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <v>-1</v>
-      </c>
-      <c r="AA5">
-        <v>-1</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30">
-      <c r="B6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D6" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" t="s">
-        <v>67</v>
       </c>
       <c r="F6">
         <v>10001</v>
       </c>
       <c r="G6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1916,72 +1942,75 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L6" t="s">
-        <v>70</v>
-      </c>
-      <c r="M6" t="b">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="M6" t="s">
+        <v>73</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
       </c>
-      <c r="P6">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>71</v>
-      </c>
-      <c r="S6" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6">
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6" t="s">
+        <v>74</v>
+      </c>
+      <c r="T6" t="b">
         <v>0</v>
       </c>
       <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
         <v>0.5</v>
       </c>
-      <c r="V6" t="b">
-        <v>0</v>
-      </c>
       <c r="W6" t="b">
         <v>0</v>
       </c>
-      <c r="Y6">
+      <c r="X6" t="b">
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AA6">
         <v>-1</v>
       </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30">
+      <c r="AB6">
+        <v>-1</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31">
       <c r="B7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F7">
         <v>10001</v>
       </c>
       <c r="G7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1990,300 +2019,312 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L7" t="s">
-        <v>70</v>
-      </c>
-      <c r="M7" t="b">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="M7" t="s">
+        <v>73</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
       </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="Q7" t="s">
+      <c r="O7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7" t="s">
+        <v>74</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0.5</v>
+      </c>
+      <c r="W7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>-1</v>
+      </c>
+      <c r="AB7">
+        <v>-1</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31">
+      <c r="A8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="R8"/>
+      <c r="W8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>-1</v>
+      </c>
+      <c r="AB8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31">
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" t="s">
         <v>71</v>
       </c>
-      <c r="S7" t="b">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
+      <c r="M9" t="s">
+        <v>73</v>
+      </c>
+      <c r="N9" t="b">
+        <v>1</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9" t="s">
+        <v>81</v>
+      </c>
+      <c r="R9" t="s">
+        <v>74</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9">
         <v>0.5</v>
       </c>
-      <c r="V7" t="b">
-        <v>0</v>
-      </c>
-      <c r="W7" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>-1</v>
-      </c>
-      <c r="AA7">
-        <v>-1</v>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30">
-      <c r="A8" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="Q8"/>
-      <c r="V8" t="b">
-        <v>0</v>
-      </c>
-      <c r="Y8">
-        <v>0</v>
-      </c>
-      <c r="Z8">
-        <v>-1</v>
-      </c>
-      <c r="AA8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30">
-      <c r="B9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9" t="s">
-        <v>49</v>
-      </c>
-      <c r="K9" t="s">
-        <v>69</v>
-      </c>
-      <c r="M9" t="b">
-        <v>1</v>
-      </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>71</v>
-      </c>
-      <c r="R9" t="b">
-        <v>1</v>
-      </c>
-      <c r="S9" t="b">
-        <v>0</v>
-      </c>
-      <c r="U9">
-        <v>0.5</v>
-      </c>
-      <c r="V9" t="b">
-        <v>0</v>
-      </c>
       <c r="W9" t="b">
         <v>0</v>
       </c>
-      <c r="Y9">
+      <c r="X9" t="b">
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AA9">
         <v>-1</v>
       </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30">
-      <c r="Q10"/>
-    </row>
-    <row r="11" spans="1:30">
+      <c r="AB9">
+        <v>-1</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31">
+      <c r="R10"/>
+    </row>
+    <row r="11" spans="1:31">
       <c r="B11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="F11">
         <v>10000</v>
       </c>
       <c r="G11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I11">
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>49</v>
-      </c>
-      <c r="M11" t="b">
-        <v>1</v>
+        <v>50</v>
+      </c>
+      <c r="M11" t="s">
+        <v>73</v>
       </c>
       <c r="N11" t="b">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>82</v>
-      </c>
-      <c r="P11">
-        <v>1</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>71</v>
-      </c>
-      <c r="R11" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+      <c r="P11" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11" t="s">
+        <v>74</v>
       </c>
       <c r="S11" t="b">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>1</v>
+      <c r="T11" t="b">
+        <v>0</v>
       </c>
       <c r="U11">
+        <v>1</v>
+      </c>
+      <c r="V11">
         <v>0.5</v>
       </c>
-      <c r="V11" t="b">
-        <v>0</v>
-      </c>
       <c r="W11" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y11">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="X11" t="b">
+        <v>1</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AA11">
         <v>-1</v>
       </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:30">
+      <c r="AB11">
+        <v>-1</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31">
       <c r="B12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E12" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F12">
         <v>10000</v>
       </c>
       <c r="G12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
+        <v>50</v>
+      </c>
+      <c r="K12" t="s">
+        <v>71</v>
+      </c>
+      <c r="L12" t="s">
+        <v>72</v>
+      </c>
+      <c r="M12" t="s">
+        <v>73</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12" t="s">
         <v>85</v>
       </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>1</v>
-      </c>
-      <c r="J12" t="s">
-        <v>49</v>
-      </c>
-      <c r="K12" t="s">
-        <v>69</v>
-      </c>
-      <c r="L12" t="s">
-        <v>70</v>
-      </c>
-      <c r="M12" t="b">
-        <v>0</v>
-      </c>
-      <c r="N12" t="b">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>82</v>
-      </c>
-      <c r="P12">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>71</v>
-      </c>
-      <c r="R12" t="b">
-        <v>0</v>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12" t="s">
+        <v>74</v>
       </c>
       <c r="S12" t="b">
-        <v>1</v>
-      </c>
-      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="T12" t="b">
+        <v>1</v>
+      </c>
+      <c r="V12">
         <v>0.5</v>
       </c>
-      <c r="V12" t="b">
-        <v>0</v>
-      </c>
       <c r="W12" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y12">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="X12" t="b">
+        <v>1</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AA12">
         <v>-1</v>
       </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:30">
+      <c r="AB12">
+        <v>-1</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31">
       <c r="B13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F13">
         <v>10000</v>
       </c>
       <c r="G13" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -2292,69 +2333,72 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L13" t="s">
-        <v>88</v>
-      </c>
-      <c r="M13" t="b">
-        <v>0</v>
+        <v>91</v>
+      </c>
+      <c r="M13" t="s">
+        <v>73</v>
       </c>
       <c r="N13" t="b">
         <v>0</v>
       </c>
-      <c r="P13">
-        <v>1</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>71</v>
-      </c>
-      <c r="R13" t="b">
-        <v>0</v>
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13" t="s">
+        <v>74</v>
       </c>
       <c r="S13" t="b">
         <v>0</v>
       </c>
-      <c r="U13">
+      <c r="T13" t="b">
+        <v>0</v>
+      </c>
+      <c r="V13">
         <v>0.5</v>
       </c>
-      <c r="V13" t="b">
-        <v>0</v>
-      </c>
       <c r="W13" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="X13" t="b">
+        <v>1</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AA13">
         <v>-1</v>
       </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:30">
+      <c r="AB13">
+        <v>-1</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31">
       <c r="B14" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E14" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F14">
         <v>10000</v>
       </c>
       <c r="G14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2363,69 +2407,72 @@
         <v>1</v>
       </c>
       <c r="J14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K14" t="s">
-        <v>69</v>
-      </c>
-      <c r="M14" t="b">
-        <v>1</v>
+        <v>71</v>
+      </c>
+      <c r="M14" t="s">
+        <v>73</v>
       </c>
       <c r="N14" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>82</v>
-      </c>
-      <c r="P14">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>71</v>
-      </c>
-      <c r="R14" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O14" t="b">
+        <v>0</v>
+      </c>
+      <c r="P14" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
+      </c>
+      <c r="R14" t="s">
+        <v>74</v>
       </c>
       <c r="S14" t="b">
         <v>0</v>
       </c>
-      <c r="U14">
+      <c r="T14" t="b">
+        <v>0</v>
+      </c>
+      <c r="V14">
         <v>0.5</v>
       </c>
-      <c r="V14" t="b">
-        <v>0</v>
-      </c>
       <c r="W14" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y14">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="X14" t="b">
+        <v>1</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AA14">
         <v>-1</v>
       </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:30">
+      <c r="AB14">
+        <v>-1</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31">
       <c r="B15" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E15" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F15">
         <v>10000</v>
       </c>
       <c r="G15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -2434,55 +2481,58 @@
         <v>1</v>
       </c>
       <c r="J15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K15" t="s">
-        <v>69</v>
-      </c>
-      <c r="M15" t="b">
-        <v>1</v>
+        <v>71</v>
+      </c>
+      <c r="M15" t="s">
+        <v>73</v>
       </c>
       <c r="N15" t="b">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>82</v>
-      </c>
-      <c r="P15">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>71</v>
-      </c>
-      <c r="R15" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O15" t="b">
+        <v>0</v>
+      </c>
+      <c r="P15" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q15">
+        <v>1</v>
+      </c>
+      <c r="R15" t="s">
+        <v>74</v>
       </c>
       <c r="S15" t="b">
         <v>0</v>
       </c>
-      <c r="U15">
+      <c r="T15" t="b">
+        <v>0</v>
+      </c>
+      <c r="V15">
         <v>0.5</v>
       </c>
-      <c r="V15" t="b">
-        <v>0</v>
-      </c>
       <c r="W15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y15">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="X15" t="b">
+        <v>1</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AA15">
         <v>-1</v>
       </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:30">
+      <c r="AB15">
+        <v>-1</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31">
       <c r="B16"/>
       <c r="C16"/>
       <c r="E16"/>
@@ -2491,29 +2541,29 @@
       <c r="H16"/>
       <c r="I16"/>
       <c r="K16"/>
-      <c r="M16"/>
       <c r="N16"/>
       <c r="O16"/>
       <c r="P16"/>
       <c r="Q16"/>
-      <c r="U16"/>
+      <c r="R16"/>
       <c r="V16"/>
-    </row>
-    <row r="17" spans="2:30">
+      <c r="W16"/>
+    </row>
+    <row r="17" spans="2:31">
       <c r="B17" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E17" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F17">
         <v>10000</v>
       </c>
       <c r="G17" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -2522,70 +2572,73 @@
         <v>1</v>
       </c>
       <c r="J17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K17" t="s">
-        <v>69</v>
-      </c>
-      <c r="M17" t="b">
-        <v>1</v>
+        <v>71</v>
+      </c>
+      <c r="M17" t="s">
+        <v>73</v>
       </c>
       <c r="N17" t="b">
-        <v>0</v>
-      </c>
-      <c r="O17"/>
-      <c r="P17">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>71</v>
-      </c>
-      <c r="R17" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O17" t="b">
+        <v>0</v>
+      </c>
+      <c r="P17"/>
+      <c r="Q17">
+        <v>1</v>
+      </c>
+      <c r="R17" t="s">
+        <v>74</v>
       </c>
       <c r="S17" t="b">
         <v>0</v>
       </c>
-      <c r="U17">
+      <c r="T17" t="b">
+        <v>0</v>
+      </c>
+      <c r="V17">
         <v>0.5</v>
       </c>
-      <c r="V17" t="b">
-        <v>0</v>
-      </c>
       <c r="W17" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="X17" t="b">
+        <v>1</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AA17">
         <v>-1</v>
       </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:30">
-      <c r="Q18"/>
-    </row>
-    <row r="19" spans="2:30">
+      <c r="AB17">
+        <v>-1</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:31">
+      <c r="R18"/>
+    </row>
+    <row r="19" spans="2:31">
       <c r="B19" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E19" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F19">
         <v>300</v>
       </c>
       <c r="G19" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H19">
         <v>6</v>
@@ -2594,72 +2647,75 @@
         <v>3</v>
       </c>
       <c r="J19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K19" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L19" t="s">
+        <v>103</v>
+      </c>
+      <c r="M19" t="s">
+        <v>73</v>
+      </c>
+      <c r="N19" t="b">
+        <v>0</v>
+      </c>
+      <c r="O19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19" t="s">
+        <v>104</v>
+      </c>
+      <c r="T19" t="b">
+        <v>1</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0.5</v>
+      </c>
+      <c r="W19" t="b">
+        <v>1</v>
+      </c>
+      <c r="X19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>-1</v>
+      </c>
+      <c r="AB19">
+        <v>-1</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:31">
+      <c r="B20" t="s">
+        <v>105</v>
+      </c>
+      <c r="C20" t="s">
         <v>100</v>
       </c>
-      <c r="M19" t="b">
-        <v>0</v>
-      </c>
-      <c r="N19" t="b">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="s">
+      <c r="E20" t="s">
         <v>101</v>
-      </c>
-      <c r="S19" t="b">
-        <v>1</v>
-      </c>
-      <c r="T19">
-        <v>0</v>
-      </c>
-      <c r="U19">
-        <v>0.5</v>
-      </c>
-      <c r="V19" t="b">
-        <v>1</v>
-      </c>
-      <c r="W19" t="b">
-        <v>0</v>
-      </c>
-      <c r="X19" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y19">
-        <v>0</v>
-      </c>
-      <c r="Z19">
-        <v>-1</v>
-      </c>
-      <c r="AA19">
-        <v>-1</v>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:30">
-      <c r="B20" t="s">
-        <v>102</v>
-      </c>
-      <c r="C20" t="s">
-        <v>97</v>
-      </c>
-      <c r="E20" t="s">
-        <v>98</v>
       </c>
       <c r="F20">
         <v>301</v>
       </c>
       <c r="G20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H20">
         <v>6</v>
@@ -2668,72 +2724,75 @@
         <v>3</v>
       </c>
       <c r="J20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K20" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L20" t="s">
+        <v>103</v>
+      </c>
+      <c r="M20" t="s">
+        <v>73</v>
+      </c>
+      <c r="N20" t="b">
+        <v>0</v>
+      </c>
+      <c r="O20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20" t="s">
+        <v>104</v>
+      </c>
+      <c r="T20" t="b">
+        <v>1</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0.5</v>
+      </c>
+      <c r="W20" t="b">
+        <v>1</v>
+      </c>
+      <c r="X20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>-1</v>
+      </c>
+      <c r="AB20">
+        <v>-1</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:31">
+      <c r="B21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" t="s">
         <v>100</v>
       </c>
-      <c r="M20" t="b">
-        <v>0</v>
-      </c>
-      <c r="N20" t="b">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="s">
+      <c r="E21" t="s">
         <v>101</v>
-      </c>
-      <c r="S20" t="b">
-        <v>1</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0.5</v>
-      </c>
-      <c r="V20" t="b">
-        <v>1</v>
-      </c>
-      <c r="W20" t="b">
-        <v>0</v>
-      </c>
-      <c r="X20" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
-      <c r="Z20">
-        <v>-1</v>
-      </c>
-      <c r="AA20">
-        <v>-1</v>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:30">
-      <c r="B21" t="s">
-        <v>103</v>
-      </c>
-      <c r="C21" t="s">
-        <v>97</v>
-      </c>
-      <c r="E21" t="s">
-        <v>98</v>
       </c>
       <c r="F21">
         <v>302</v>
       </c>
       <c r="G21" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H21">
         <v>6</v>
@@ -2742,75 +2801,78 @@
         <v>3</v>
       </c>
       <c r="J21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K21" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L21" t="s">
+        <v>103</v>
+      </c>
+      <c r="M21" t="s">
+        <v>73</v>
+      </c>
+      <c r="N21" t="b">
+        <v>0</v>
+      </c>
+      <c r="O21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21" t="s">
+        <v>104</v>
+      </c>
+      <c r="T21" t="b">
+        <v>1</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0.5</v>
+      </c>
+      <c r="W21" t="b">
+        <v>1</v>
+      </c>
+      <c r="X21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>-1</v>
+      </c>
+      <c r="AB21">
+        <v>-1</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:31">
+      <c r="R22"/>
+    </row>
+    <row r="23" spans="2:31">
+      <c r="B23" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" t="s">
         <v>100</v>
       </c>
-      <c r="M21" t="b">
-        <v>0</v>
-      </c>
-      <c r="N21" t="b">
-        <v>0</v>
-      </c>
-      <c r="P21">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>101</v>
-      </c>
-      <c r="S21" t="b">
-        <v>1</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0.5</v>
-      </c>
-      <c r="V21" t="b">
-        <v>1</v>
-      </c>
-      <c r="W21" t="b">
-        <v>0</v>
-      </c>
-      <c r="X21" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>-1</v>
-      </c>
-      <c r="AA21">
-        <v>-1</v>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:30">
-      <c r="Q22"/>
-    </row>
-    <row r="23" spans="2:30">
-      <c r="B23" t="s">
-        <v>104</v>
-      </c>
-      <c r="C23" t="s">
-        <v>97</v>
-      </c>
       <c r="E23" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F23">
         <v>400</v>
       </c>
       <c r="G23" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H23">
         <v>6</v>
@@ -2819,72 +2881,75 @@
         <v>3</v>
       </c>
       <c r="J23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K23" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L23" t="s">
+        <v>103</v>
+      </c>
+      <c r="M23" t="s">
+        <v>73</v>
+      </c>
+      <c r="N23" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23" t="s">
+        <v>104</v>
+      </c>
+      <c r="T23" t="b">
+        <v>1</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0.5</v>
+      </c>
+      <c r="W23" t="b">
+        <v>1</v>
+      </c>
+      <c r="X23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>-1</v>
+      </c>
+      <c r="AB23">
+        <v>-1</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:31">
+      <c r="B24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C24" t="s">
         <v>100</v>
       </c>
-      <c r="M23" t="b">
-        <v>0</v>
-      </c>
-      <c r="N23" t="b">
-        <v>0</v>
-      </c>
-      <c r="P23">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>101</v>
-      </c>
-      <c r="S23" t="b">
-        <v>1</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0.5</v>
-      </c>
-      <c r="V23" t="b">
-        <v>1</v>
-      </c>
-      <c r="W23" t="b">
-        <v>0</v>
-      </c>
-      <c r="X23" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y23">
-        <v>0</v>
-      </c>
-      <c r="Z23">
-        <v>-1</v>
-      </c>
-      <c r="AA23">
-        <v>-1</v>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:30">
-      <c r="B24" t="s">
-        <v>106</v>
-      </c>
-      <c r="C24" t="s">
-        <v>97</v>
-      </c>
       <c r="E24" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F24">
         <v>401</v>
       </c>
       <c r="G24" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H24">
         <v>6</v>
@@ -2893,72 +2958,75 @@
         <v>3</v>
       </c>
       <c r="J24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K24" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L24" t="s">
+        <v>103</v>
+      </c>
+      <c r="M24" t="s">
+        <v>73</v>
+      </c>
+      <c r="N24" t="b">
+        <v>0</v>
+      </c>
+      <c r="O24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24" t="s">
+        <v>104</v>
+      </c>
+      <c r="T24" t="b">
+        <v>1</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0.5</v>
+      </c>
+      <c r="W24" t="b">
+        <v>1</v>
+      </c>
+      <c r="X24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>-1</v>
+      </c>
+      <c r="AB24">
+        <v>-1</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:31">
+      <c r="B25" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" t="s">
         <v>100</v>
       </c>
-      <c r="M24" t="b">
-        <v>0</v>
-      </c>
-      <c r="N24" t="b">
-        <v>0</v>
-      </c>
-      <c r="P24">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>101</v>
-      </c>
-      <c r="S24" t="b">
-        <v>1</v>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>0.5</v>
-      </c>
-      <c r="V24" t="b">
-        <v>1</v>
-      </c>
-      <c r="W24" t="b">
-        <v>0</v>
-      </c>
-      <c r="X24" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y24">
-        <v>0</v>
-      </c>
-      <c r="Z24">
-        <v>-1</v>
-      </c>
-      <c r="AA24">
-        <v>-1</v>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:30">
-      <c r="B25" t="s">
-        <v>107</v>
-      </c>
-      <c r="C25" t="s">
-        <v>97</v>
-      </c>
       <c r="E25" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F25">
         <v>402</v>
       </c>
       <c r="G25" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H25">
         <v>6</v>
@@ -2967,75 +3035,78 @@
         <v>3</v>
       </c>
       <c r="J25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K25" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L25" t="s">
+        <v>103</v>
+      </c>
+      <c r="M25" t="s">
+        <v>73</v>
+      </c>
+      <c r="N25" t="b">
+        <v>0</v>
+      </c>
+      <c r="O25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25" t="s">
+        <v>104</v>
+      </c>
+      <c r="T25" t="b">
+        <v>1</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0.5</v>
+      </c>
+      <c r="W25" t="b">
+        <v>1</v>
+      </c>
+      <c r="X25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>-1</v>
+      </c>
+      <c r="AB25">
+        <v>-1</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:31">
+      <c r="R26"/>
+    </row>
+    <row r="27" spans="2:31">
+      <c r="B27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" t="s">
         <v>100</v>
       </c>
-      <c r="M25" t="b">
-        <v>0</v>
-      </c>
-      <c r="N25" t="b">
-        <v>0</v>
-      </c>
-      <c r="P25">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>101</v>
-      </c>
-      <c r="S25" t="b">
-        <v>1</v>
-      </c>
-      <c r="T25">
-        <v>0</v>
-      </c>
-      <c r="U25">
-        <v>0.5</v>
-      </c>
-      <c r="V25" t="b">
-        <v>1</v>
-      </c>
-      <c r="W25" t="b">
-        <v>0</v>
-      </c>
-      <c r="X25" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y25">
-        <v>0</v>
-      </c>
-      <c r="Z25">
-        <v>-1</v>
-      </c>
-      <c r="AA25">
-        <v>-1</v>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:30">
-      <c r="Q26"/>
-    </row>
-    <row r="27" spans="2:30">
-      <c r="B27" t="s">
-        <v>108</v>
-      </c>
-      <c r="C27" t="s">
-        <v>97</v>
-      </c>
       <c r="E27" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F27">
         <v>501</v>
       </c>
       <c r="G27" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H27">
         <v>6</v>
@@ -3044,72 +3115,75 @@
         <v>3</v>
       </c>
       <c r="J27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K27" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L27" t="s">
+        <v>103</v>
+      </c>
+      <c r="M27" t="s">
+        <v>73</v>
+      </c>
+      <c r="N27" t="b">
+        <v>0</v>
+      </c>
+      <c r="O27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27" t="s">
+        <v>104</v>
+      </c>
+      <c r="T27" t="b">
+        <v>1</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0.5</v>
+      </c>
+      <c r="W27" t="b">
+        <v>1</v>
+      </c>
+      <c r="X27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>-1</v>
+      </c>
+      <c r="AB27">
+        <v>-1</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:31">
+      <c r="B28" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" t="s">
         <v>100</v>
       </c>
-      <c r="M27" t="b">
-        <v>0</v>
-      </c>
-      <c r="N27" t="b">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>101</v>
-      </c>
-      <c r="S27" t="b">
-        <v>1</v>
-      </c>
-      <c r="T27">
-        <v>0</v>
-      </c>
-      <c r="U27">
-        <v>0.5</v>
-      </c>
-      <c r="V27" t="b">
-        <v>1</v>
-      </c>
-      <c r="W27" t="b">
-        <v>0</v>
-      </c>
-      <c r="X27" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y27">
-        <v>0</v>
-      </c>
-      <c r="Z27">
-        <v>-1</v>
-      </c>
-      <c r="AA27">
-        <v>-1</v>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:30">
-      <c r="B28" t="s">
-        <v>110</v>
-      </c>
-      <c r="C28" t="s">
-        <v>97</v>
-      </c>
       <c r="E28" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F28">
         <v>502</v>
       </c>
       <c r="G28" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H28">
         <v>6</v>
@@ -3118,72 +3192,75 @@
         <v>3</v>
       </c>
       <c r="J28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K28" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L28" t="s">
+        <v>103</v>
+      </c>
+      <c r="M28" t="s">
+        <v>73</v>
+      </c>
+      <c r="N28" t="b">
+        <v>0</v>
+      </c>
+      <c r="O28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28" t="s">
+        <v>104</v>
+      </c>
+      <c r="T28" t="b">
+        <v>1</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0.5</v>
+      </c>
+      <c r="W28" t="b">
+        <v>1</v>
+      </c>
+      <c r="X28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>-1</v>
+      </c>
+      <c r="AB28">
+        <v>-1</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:31">
+      <c r="B29" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" t="s">
         <v>100</v>
       </c>
-      <c r="M28" t="b">
-        <v>0</v>
-      </c>
-      <c r="N28" t="b">
-        <v>0</v>
-      </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>101</v>
-      </c>
-      <c r="S28" t="b">
-        <v>1</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0.5</v>
-      </c>
-      <c r="V28" t="b">
-        <v>1</v>
-      </c>
-      <c r="W28" t="b">
-        <v>0</v>
-      </c>
-      <c r="X28" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y28">
-        <v>0</v>
-      </c>
-      <c r="Z28">
-        <v>-1</v>
-      </c>
-      <c r="AA28">
-        <v>-1</v>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:30">
-      <c r="B29" t="s">
-        <v>111</v>
-      </c>
-      <c r="C29" t="s">
-        <v>97</v>
-      </c>
       <c r="E29" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F29">
         <v>503</v>
       </c>
       <c r="G29" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H29">
         <v>6</v>
@@ -3192,75 +3269,78 @@
         <v>3</v>
       </c>
       <c r="J29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K29" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L29" t="s">
-        <v>100</v>
-      </c>
-      <c r="M29" t="b">
-        <v>0</v>
+        <v>103</v>
+      </c>
+      <c r="M29" t="s">
+        <v>73</v>
       </c>
       <c r="N29" t="b">
         <v>0</v>
       </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>101</v>
-      </c>
-      <c r="S29" t="b">
-        <v>1</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
+      <c r="O29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29" t="s">
+        <v>104</v>
+      </c>
+      <c r="T29" t="b">
+        <v>1</v>
       </c>
       <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
         <v>0.5</v>
       </c>
-      <c r="V29" t="b">
-        <v>1</v>
-      </c>
       <c r="W29" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X29" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y29">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Y29" t="b">
+        <v>1</v>
       </c>
       <c r="Z29">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AA29">
         <v>-1</v>
       </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:30">
-      <c r="Q30"/>
-    </row>
-    <row r="31" spans="2:30">
+      <c r="AB29">
+        <v>-1</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:31">
+      <c r="R30"/>
+    </row>
+    <row r="31" spans="2:31">
       <c r="B31" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C31" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E31" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="F31">
         <v>10000</v>
       </c>
       <c r="G31" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="H31">
         <v>0</v>
@@ -3269,72 +3349,73 @@
         <v>0</v>
       </c>
       <c r="J31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K31" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L31" t="s">
-        <v>116</v>
-      </c>
-      <c r="M31" t="b">
-        <v>1</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="M31"/>
       <c r="N31" t="b">
         <v>1</v>
       </c>
-      <c r="P31">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>101</v>
-      </c>
-      <c r="S31" t="b">
-        <v>1</v>
-      </c>
-      <c r="T31">
-        <v>0</v>
+      <c r="O31" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31" t="s">
+        <v>104</v>
+      </c>
+      <c r="T31" t="b">
+        <v>1</v>
       </c>
       <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
         <v>0.5</v>
       </c>
-      <c r="V31" t="b">
-        <v>1</v>
-      </c>
       <c r="W31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y31">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Y31" t="b">
+        <v>1</v>
       </c>
       <c r="Z31">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AA31">
         <v>-1</v>
       </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:30">
+      <c r="AB31">
+        <v>-1</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31">
       <c r="B33" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C33" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E33" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F33">
         <v>10000</v>
       </c>
       <c r="G33" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -3343,70 +3424,71 @@
         <v>0</v>
       </c>
       <c r="J33" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K33" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L33" t="s">
-        <v>70</v>
-      </c>
-      <c r="M33" t="b">
-        <v>0</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="M33"/>
       <c r="N33" t="b">
         <v>0</v>
       </c>
-      <c r="O33"/>
-      <c r="P33">
-        <v>1</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>71</v>
-      </c>
-      <c r="R33" t="b">
-        <v>0</v>
+      <c r="O33" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33"/>
+      <c r="Q33">
+        <v>1</v>
+      </c>
+      <c r="R33" t="s">
+        <v>74</v>
       </c>
       <c r="S33" t="b">
-        <v>1</v>
-      </c>
-      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="T33" t="b">
+        <v>1</v>
+      </c>
+      <c r="V33">
         <v>0.5</v>
       </c>
-      <c r="V33" t="b">
-        <v>0</v>
-      </c>
       <c r="W33" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y33">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="X33" t="b">
+        <v>1</v>
       </c>
       <c r="Z33">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AA33">
         <v>-1</v>
       </c>
-      <c r="AD33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:30">
+      <c r="AB33">
+        <v>-1</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31">
       <c r="B34" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C34" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E34" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F34">
         <v>10000</v>
       </c>
       <c r="G34" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H34">
         <v>5</v>
@@ -3415,27 +3497,28 @@
         <v>0</v>
       </c>
       <c r="J34" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K34" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="L34" t="s">
-        <v>124</v>
-      </c>
-      <c r="M34" t="b">
-        <v>0</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="M34"/>
       <c r="N34" t="b">
-        <v>1</v>
-      </c>
-      <c r="P34">
-        <v>1</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>71</v>
-      </c>
-      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="O34" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q34">
+        <v>1</v>
+      </c>
+      <c r="R34" t="s">
+        <v>74</v>
+      </c>
+      <c r="AE34" t="b">
         <v>1</v>
       </c>
     </row>
@@ -3468,107 +3551,107 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F1" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G1" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="H1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="I1" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J1" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K1" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3"/>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -3990,82 +4073,82 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C1" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F1" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="G4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="B5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -4085,7 +4168,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="B6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C6">
         <v>5000</v>
@@ -4105,7 +4188,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="B7" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C7">
         <v>15000</v>
@@ -4125,7 +4208,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="B8" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C8">
         <v>25000</v>

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="164">
   <si>
     <t>##var</t>
   </si>
@@ -419,6 +419,33 @@
   </si>
   <si>
     <t>cannon_shoot_01</t>
+  </si>
+  <si>
+    <t>homestead_elder</t>
+  </si>
+  <si>
+    <t>镇长</t>
+  </si>
+  <si>
+    <t>CharacterKey=home_elder</t>
+  </si>
+  <si>
+    <t>default_peace</t>
+  </si>
+  <si>
+    <t>homestead_elder_01</t>
+  </si>
+  <si>
+    <t>homestead_merchant</t>
+  </si>
+  <si>
+    <t>木匠</t>
+  </si>
+  <si>
+    <t>CharacterKey=home_merchant</t>
+  </si>
+  <si>
+    <t>homestead_merchant_01</t>
   </si>
   <si>
     <t>level</t>
@@ -1438,11 +1465,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AE34"/>
+  <dimension ref="A1:AE37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="24" style="1" customWidth="1"/>
     <col min="3" max="3" width="12.125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.25" customWidth="1"/>
     <col min="5" max="5" width="17.125" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.625" style="1" customWidth="1"/>
     <col min="7" max="7" width="20.625" style="1" customWidth="1"/>
@@ -3520,6 +3548,189 @@
       </c>
       <c r="AE34" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31">
+      <c r="B35"/>
+      <c r="C35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
+      <c r="H35"/>
+      <c r="I35"/>
+      <c r="J35"/>
+      <c r="K35"/>
+      <c r="L35"/>
+      <c r="M35"/>
+      <c r="N35"/>
+      <c r="O35"/>
+      <c r="Q35"/>
+      <c r="R35"/>
+    </row>
+    <row r="36" spans="2:31">
+      <c r="B36" t="s">
+        <v>128</v>
+      </c>
+      <c r="C36" t="s">
+        <v>129</v>
+      </c>
+      <c r="D36" t="s">
+        <v>130</v>
+      </c>
+      <c r="E36" t="s">
+        <v>92</v>
+      </c>
+      <c r="F36">
+        <v>10000</v>
+      </c>
+      <c r="G36" t="s">
+        <v>131</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="J36" t="s">
+        <v>50</v>
+      </c>
+      <c r="K36" t="s">
+        <v>71</v>
+      </c>
+      <c r="N36" t="b">
+        <v>1</v>
+      </c>
+      <c r="O36" t="b">
+        <v>0</v>
+      </c>
+      <c r="P36" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q36">
+        <v>0</v>
+      </c>
+      <c r="R36" t="s">
+        <v>74</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="b">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0.5</v>
+      </c>
+      <c r="W36" t="b">
+        <v>0</v>
+      </c>
+      <c r="X36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>-1</v>
+      </c>
+      <c r="AB36">
+        <v>-1</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31">
+      <c r="B37" t="s">
+        <v>133</v>
+      </c>
+      <c r="C37" t="s">
+        <v>134</v>
+      </c>
+      <c r="D37" t="s">
+        <v>135</v>
+      </c>
+      <c r="E37" t="s">
+        <v>92</v>
+      </c>
+      <c r="F37">
+        <v>10000</v>
+      </c>
+      <c r="G37" t="s">
+        <v>131</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="J37" t="s">
+        <v>50</v>
+      </c>
+      <c r="K37" t="s">
+        <v>71</v>
+      </c>
+      <c r="N37" t="b">
+        <v>1</v>
+      </c>
+      <c r="O37" t="b">
+        <v>0</v>
+      </c>
+      <c r="P37" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37" t="s">
+        <v>74</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0.5</v>
+      </c>
+      <c r="W37" t="b">
+        <v>0</v>
+      </c>
+      <c r="X37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>-1</v>
+      </c>
+      <c r="AB37">
+        <v>-1</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3551,31 +3762,31 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="D1" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="E1" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F1" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G1" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="H1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="I1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="J1" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="K1" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -3627,31 +3838,31 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="D4" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="E4" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="F4" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="G4" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="H4" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="I4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="J4" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="K4" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -4073,22 +4284,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C1" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="D1" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="E1" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="F1" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="G1" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -4140,10 +4351,10 @@
         <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="G4" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -4188,7 +4399,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="B7" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="C7">
         <v>15000</v>
@@ -4208,7 +4419,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="B8" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="C8">
         <v>25000</v>

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AF37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24" customWidth="1" style="1" min="2" max="2"/>
@@ -1180,6 +1180,21 @@
           <t>mind_tag</t>
         </is>
       </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>jingyuan_pool_id</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>fallback_drop_id</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>lock_initial_face</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -1327,6 +1342,21 @@
           <t>string</t>
         </is>
       </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -1466,6 +1496,21 @@
         </is>
       </c>
       <c r="AC3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
@@ -1616,6 +1661,21 @@
           <t>mind_tag</t>
         </is>
       </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>jingyuan_pool_id</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>fallback_drop_id</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>lock_initial_face</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="0" t="inlineStr">
@@ -1715,6 +1775,17 @@
           <t>orc_common</t>
         </is>
       </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="0" t="inlineStr">
@@ -1809,6 +1880,17 @@
       <c r="AB6" s="0" t="n">
         <v>-1</v>
       </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="0" t="inlineStr">
@@ -1903,6 +1985,17 @@
       <c r="AB7" s="0" t="n">
         <v>-1</v>
       </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
@@ -2007,6 +2100,17 @@
       <c r="AB9" s="0" t="n">
         <v>-1</v>
       </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="R10" s="0" t="n"/>
@@ -2094,6 +2198,17 @@
       <c r="AB11" s="0" t="n">
         <v>-1</v>
       </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="B12" s="0" t="inlineStr">
@@ -2188,6 +2303,17 @@
       <c r="AB12" s="0" t="n">
         <v>-1</v>
       </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="B13" s="0" t="inlineStr">
@@ -2277,6 +2403,12 @@
       <c r="AB13" s="0" t="n">
         <v>-1</v>
       </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="0" t="inlineStr">
@@ -2366,6 +2498,17 @@
       <c r="AB14" s="0" t="n">
         <v>-1</v>
       </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="0" t="inlineStr">
@@ -2454,6 +2597,17 @@
       </c>
       <c r="AB15" s="0" t="n">
         <v>-1</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2557,6 +2711,17 @@
       <c r="AB17" s="0" t="n">
         <v>-1</v>
       </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="R18" s="0" t="n"/>
@@ -2652,6 +2817,12 @@
       <c r="AB19" s="0" t="n">
         <v>-1</v>
       </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="B20" s="0" t="inlineStr">
@@ -2744,6 +2915,12 @@
       <c r="AB20" s="0" t="n">
         <v>-1</v>
       </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="B21" s="0" t="inlineStr">
@@ -2836,6 +3013,12 @@
       <c r="AB21" s="0" t="n">
         <v>-1</v>
       </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="R22" s="0" t="n"/>
@@ -2931,6 +3114,12 @@
       <c r="AB23" s="0" t="n">
         <v>-1</v>
       </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="0" t="inlineStr">
@@ -3023,6 +3212,12 @@
       <c r="AB24" s="0" t="n">
         <v>-1</v>
       </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="0" t="inlineStr">
@@ -3115,6 +3310,12 @@
       <c r="AB25" s="0" t="n">
         <v>-1</v>
       </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="R26" s="0" t="n"/>
@@ -3210,6 +3411,12 @@
       <c r="AB27" s="0" t="n">
         <v>-1</v>
       </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="0" t="inlineStr">
@@ -3302,6 +3509,12 @@
       <c r="AB28" s="0" t="n">
         <v>-1</v>
       </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="B29" s="0" t="inlineStr">
@@ -3394,6 +3607,12 @@
       <c r="AB29" s="0" t="n">
         <v>-1</v>
       </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="R30" s="0" t="n"/>
@@ -3485,7 +3704,14 @@
       <c r="AB31" s="0" t="n">
         <v>-1</v>
       </c>
-    </row>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="B33" s="0" t="inlineStr">
         <is>
@@ -3571,6 +3797,12 @@
       <c r="AB33" s="0" t="n">
         <v>-1</v>
       </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="B34" s="0" t="inlineStr">
@@ -3631,6 +3863,12 @@
         <is>
           <t>Normal</t>
         </is>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -3744,6 +3982,17 @@
       <c r="AB36" s="0" t="n">
         <v>-1</v>
       </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="B37" s="0" t="inlineStr">
@@ -3838,6 +4087,17 @@
       </c>
       <c r="AB37" s="0" t="n">
         <v>-1</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF37"/>
+  <dimension ref="A1:AI37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24" customWidth="1" style="1" min="2" max="2"/>
@@ -1180,19 +1180,24 @@
           <t>mind_tag</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="0" t="inlineStr">
         <is>
           <t>jingyuan_pool_id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="0" t="inlineStr">
         <is>
           <t>fallback_drop_id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="0" t="inlineStr">
         <is>
           <t>lock_initial_face</t>
+        </is>
+      </c>
+      <c r="AG1" s="0" t="inlineStr">
+        <is>
+          <t>race_id</t>
         </is>
       </c>
     </row>
@@ -1342,19 +1347,29 @@
           <t>string</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AF2" s="0" t="inlineStr">
         <is>
           <t>bool</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AH2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
         </is>
       </c>
     </row>
@@ -1500,17 +1515,27 @@
           <t>c,s</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AF3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="AI3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
@@ -1661,21 +1686,22 @@
           <t>mind_tag</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD4" s="0" t="inlineStr">
         <is>
           <t>jingyuan_pool_id</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AE4" s="0" t="inlineStr">
         <is>
           <t>fallback_drop_id</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AF4" s="0" t="inlineStr">
         <is>
           <t>lock_initial_face</t>
         </is>
       </c>
+      <c r="AG4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="B5" s="0" t="inlineStr">
@@ -1775,16 +1801,21 @@
           <t>orc_common</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD5" s="0" t="inlineStr">
         <is>
           <t>orc</t>
         </is>
       </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="b">
-        <v>0</v>
+      <c r="AE5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="0" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1880,16 +1911,21 @@
       <c r="AB6" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AD6" s="0" t="inlineStr">
         <is>
           <t>orc</t>
         </is>
       </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="b">
-        <v>0</v>
+      <c r="AE6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="0" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1985,16 +2021,21 @@
       <c r="AB7" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AD7" s="0" t="inlineStr">
         <is>
           <t>orc</t>
         </is>
       </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="b">
-        <v>0</v>
+      <c r="AE7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="0" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -2019,6 +2060,7 @@
       <c r="AB8" s="0" t="n">
         <v>-1</v>
       </c>
+      <c r="AG8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="0" t="inlineStr">
@@ -2100,20 +2142,26 @@
       <c r="AB9" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AD9" s="0" t="inlineStr">
         <is>
           <t>human</t>
         </is>
       </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="b">
-        <v>0</v>
+      <c r="AE9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="R10" s="0" t="n"/>
+      <c r="AG10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="0" t="inlineStr">
@@ -2198,16 +2246,21 @@
       <c r="AB11" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AD11" s="0" t="inlineStr">
         <is>
           <t>human</t>
         </is>
       </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="b">
-        <v>0</v>
+      <c r="AE11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -2303,16 +2356,21 @@
       <c r="AB12" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AD12" s="0" t="inlineStr">
         <is>
           <t>human</t>
         </is>
       </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="b">
-        <v>0</v>
+      <c r="AE12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -2403,12 +2461,13 @@
       <c r="AB13" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="B14" s="0" t="inlineStr">
@@ -2498,16 +2557,21 @@
       <c r="AB14" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AD14" t="inlineStr">
+      <c r="AD14" s="0" t="inlineStr">
         <is>
           <t>human</t>
         </is>
       </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" t="b">
-        <v>0</v>
+      <c r="AE14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -2598,16 +2662,21 @@
       <c r="AB15" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AD15" t="inlineStr">
+      <c r="AD15" s="0" t="inlineStr">
         <is>
           <t>human</t>
         </is>
       </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="b">
-        <v>0</v>
+      <c r="AE15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -2626,6 +2695,7 @@
       <c r="R16" s="0" t="n"/>
       <c r="V16" s="0" t="n"/>
       <c r="W16" s="0" t="n"/>
+      <c r="AG16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" s="0" t="inlineStr">
@@ -2711,20 +2781,26 @@
       <c r="AB17" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AD17" t="inlineStr">
+      <c r="AD17" s="0" t="inlineStr">
         <is>
           <t>human</t>
         </is>
       </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="b">
-        <v>0</v>
+      <c r="AE17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="R18" s="0" t="n"/>
+      <c r="AG18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="0" t="inlineStr">
@@ -2817,12 +2893,13 @@
       <c r="AB19" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" s="0" t="inlineStr">
@@ -2915,12 +2992,13 @@
       <c r="AB20" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="0" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" s="0" t="inlineStr">
@@ -3013,15 +3091,17 @@
       <c r="AB21" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="0" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="R22" s="0" t="n"/>
+      <c r="AG22" s="0" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="B23" s="0" t="inlineStr">
@@ -3114,12 +3194,13 @@
       <c r="AB23" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="0" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="B24" s="0" t="inlineStr">
@@ -3212,12 +3293,13 @@
       <c r="AB24" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="0" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="B25" s="0" t="inlineStr">
@@ -3310,15 +3392,17 @@
       <c r="AB25" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="0" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="R26" s="0" t="n"/>
+      <c r="AG26" s="0" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="B27" s="0" t="inlineStr">
@@ -3411,12 +3495,13 @@
       <c r="AB27" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="0" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="B28" s="0" t="inlineStr">
@@ -3509,12 +3594,13 @@
       <c r="AB28" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="0" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="B29" s="0" t="inlineStr">
@@ -3607,15 +3693,17 @@
       <c r="AB29" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="0" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="R30" s="0" t="n"/>
+      <c r="AG30" s="0" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="B31" s="0" t="inlineStr">
@@ -3704,14 +3792,17 @@
       <c r="AB31" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32"/>
+      <c r="AE31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="0" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="AG32" s="0" t="inlineStr"/>
+    </row>
     <row r="33">
       <c r="B33" s="0" t="inlineStr">
         <is>
@@ -3797,12 +3888,13 @@
       <c r="AB33" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="b">
-        <v>0</v>
-      </c>
+      <c r="AE33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="0" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="B34" s="0" t="inlineStr">
@@ -3864,12 +3956,13 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="b">
-        <v>1</v>
-      </c>
+      <c r="AE34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG34" s="0" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="B35" s="0" t="n"/>
@@ -3887,6 +3980,7 @@
       <c r="O35" s="0" t="n"/>
       <c r="Q35" s="0" t="n"/>
       <c r="R35" s="0" t="n"/>
+      <c r="AG35" s="0" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" s="0" t="inlineStr">
@@ -3982,16 +4076,21 @@
       <c r="AB36" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AD36" t="inlineStr">
+      <c r="AD36" s="0" t="inlineStr">
         <is>
           <t>human</t>
         </is>
       </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="b">
-        <v>0</v>
+      <c r="AE36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -4088,16 +4187,21 @@
       <c r="AB37" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AD37" t="inlineStr">
+      <c r="AD37" s="0" t="inlineStr">
         <is>
           <t>human</t>
         </is>
       </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="b">
-        <v>0</v>
+      <c r="AE37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="unit_npc" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="unit_npc_attribute" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="desire_density_info" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_npc" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_npc_attribute" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="desire_density_info" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI37"/>
+  <dimension ref="A1:AI38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24" customWidth="1" style="1" min="2" max="2"/>
@@ -1362,7 +1362,7 @@
           <t>bool</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -1530,7 +1530,7 @@
           <t>c,s</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
@@ -4204,6 +4204,101 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>forest_fly_swarm</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t>飞虫群</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="inlineStr">
+        <is>
+          <t>森林中的小型飞虫群</t>
+        </is>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>evil_child</t>
+        </is>
+      </c>
+      <c r="F38" s="0" t="n">
+        <v>10020</v>
+      </c>
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t>default_monster</t>
+        </is>
+      </c>
+      <c r="H38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J38" s="0" t="inlineStr">
+        <is>
+          <t>NoMove</t>
+        </is>
+      </c>
+      <c r="K38" s="0" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="L38" s="0" t="inlineStr">
+        <is>
+          <t>forest_fly_attach</t>
+        </is>
+      </c>
+      <c r="N38" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O38" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" s="0" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="S38" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V38" s="0" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="W38" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X38" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB38" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AE38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -4216,7 +4311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="18.75" customWidth="1" style="1" min="2" max="3"/>
@@ -4801,6 +4896,38 @@
       </c>
       <c r="J21" s="0" t="n">
         <v>999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="0" t="n">
+        <v>10020</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="E22" s="0" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F22" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI38"/>
+  <dimension ref="A1:AI40"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24" customWidth="1" style="1" min="2" max="2"/>
@@ -1200,6 +1200,11 @@
           <t>race_id</t>
         </is>
       </c>
+      <c r="AH1" s="0" t="inlineStr">
+        <is>
+          <t>npc_tags</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -1369,7 +1374,7 @@
       </c>
       <c r="AH2" s="0" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>(list#sep=|);string</t>
         </is>
       </c>
     </row>
@@ -1535,11 +1540,12 @@
           <t>c,s</t>
         </is>
       </c>
-      <c r="AI3" s="0" t="inlineStr">
+      <c r="AH3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
+      <c r="AI3" s="0" t="n"/>
     </row>
     <row r="4" ht="81" customHeight="1" s="1">
       <c r="A4" s="0" t="inlineStr">
@@ -1702,6 +1708,11 @@
         </is>
       </c>
       <c r="AG4" s="0" t="inlineStr"/>
+      <c r="AH4" s="0" t="inlineStr">
+        <is>
+          <t>Common NPC content tags for drop pools, recipe pools, and other content matching.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="0" t="inlineStr">
@@ -1817,6 +1828,11 @@
           <t>orc</t>
         </is>
       </c>
+      <c r="AH5" s="0" t="inlineStr">
+        <is>
+          <t>orc_common</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="0" t="inlineStr">
@@ -2070,7 +2086,12 @@
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>卢卡</t>
+          <t>卡莱尔</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>CharacterKey=carlisle; state=unconscious; legacy scene id</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
@@ -2110,7 +2131,7 @@
       </c>
       <c r="P9" s="0" t="inlineStr">
         <is>
-          <t>game_init_luca_injured</t>
+          <t>carlisle_unconscious_entry</t>
         </is>
       </c>
       <c r="R9" s="0" t="inlineStr">
@@ -4204,7 +4225,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" s="1">
       <c r="B38" s="0" t="inlineStr">
         <is>
           <t>forest_fly_swarm</t>
@@ -4297,6 +4318,240 @@
       </c>
       <c r="AF38" s="0" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="39" s="1">
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t>game_init_carlisle_unconscious</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>卡莱尔</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="inlineStr">
+        <is>
+          <t>CharacterKey=carlisle; state=unconscious</t>
+        </is>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>game_init_luca_injured</t>
+        </is>
+      </c>
+      <c r="F39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="0" t="inlineStr"/>
+      <c r="H39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="0" t="inlineStr">
+        <is>
+          <t>NoMove</t>
+        </is>
+      </c>
+      <c r="K39" s="0" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="L39" s="0" t="inlineStr"/>
+      <c r="M39" s="0" t="inlineStr"/>
+      <c r="N39" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O39" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P39" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_unconscious_entry</t>
+        </is>
+      </c>
+      <c r="Q39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="0" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="S39" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W39" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X39" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB39" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC39" s="0" t="inlineStr"/>
+      <c r="AD39" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AE39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AH39" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" s="1">
+      <c r="B40" s="0" t="inlineStr">
+        <is>
+          <t>game_init_carlisle_awake</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>卡莱尔</t>
+        </is>
+      </c>
+      <c r="D40" s="0" t="inlineStr">
+        <is>
+          <t>CharacterKey=carlisle; state=awake</t>
+        </is>
+      </c>
+      <c r="E40" s="0" t="inlineStr">
+        <is>
+          <t>civil</t>
+        </is>
+      </c>
+      <c r="F40" s="0" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G40" s="0" t="inlineStr">
+        <is>
+          <t>default_peace</t>
+        </is>
+      </c>
+      <c r="H40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="0" t="inlineStr">
+        <is>
+          <t>NoMove</t>
+        </is>
+      </c>
+      <c r="K40" s="0" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="L40" s="0" t="inlineStr"/>
+      <c r="M40" s="0" t="inlineStr"/>
+      <c r="N40" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O40" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P40" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_awake_entry</t>
+        </is>
+      </c>
+      <c r="Q40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="0" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="S40" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W40" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X40" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB40" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC40" s="0" t="inlineStr"/>
+      <c r="AD40" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AE40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AH40" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_npc" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_npc_attribute" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="desire_density_info" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="unit_npc" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="unit_npc_attribute" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="desire_density_info" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI40"/>
+  <dimension ref="A1:AI41"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24" customWidth="1" style="1" min="2" max="2"/>
@@ -4011,12 +4011,12 @@
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>镇长</t>
+          <t>埃蒙</t>
         </is>
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
-          <t>CharacterKey=home_elder</t>
+          <t>CharacterKey=home_elder; reliable elder; surveyor traces</t>
         </is>
       </c>
       <c r="E36" s="0" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>木匠</t>
+          <t>灰露棚看管人</t>
         </is>
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
-          <t>CharacterKey=home_merchant</t>
+          <t>CharacterKey=home_merchant; gray-dew shed and hearth handler</t>
         </is>
       </c>
       <c r="E37" s="0" t="inlineStr">
@@ -4551,6 +4551,126 @@
       <c r="AH40" s="0" t="inlineStr">
         <is>
           <t>human</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t>home_robber_n</t>
+        </is>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t>流匪冒险者</t>
+        </is>
+      </c>
+      <c r="D41" s="0" t="inlineStr">
+        <is>
+          <t>First-act robber adventurer placeholder; linked to Marlock gang.</t>
+        </is>
+      </c>
+      <c r="E41" s="0" t="inlineStr">
+        <is>
+          <t>initial_orc</t>
+        </is>
+      </c>
+      <c r="F41" s="0" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G41" s="0" t="inlineStr">
+        <is>
+          <t>default_npc</t>
+        </is>
+      </c>
+      <c r="H41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="0" t="inlineStr">
+        <is>
+          <t>NoMove</t>
+        </is>
+      </c>
+      <c r="K41" s="0" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="L41" s="0" t="inlineStr">
+        <is>
+          <t>default_normal_attack</t>
+        </is>
+      </c>
+      <c r="M41" s="0" t="inlineStr">
+        <is>
+          <t>default_h_attack|default_enemy_harass|default_enemy_knockdown_push</t>
+        </is>
+      </c>
+      <c r="N41" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O41" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R41" s="0" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="T41" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W41" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X41" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB41" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AC41" s="0" t="inlineStr">
+        <is>
+          <t>human_bandit</t>
+        </is>
+      </c>
+      <c r="AD41" s="0" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="AE41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AH41" s="0" t="inlineStr">
+        <is>
+          <t>bandit|human</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -1010,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI41"/>
+  <dimension ref="A1:AL44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24" customWidth="1" style="1" min="2" max="2"/>
@@ -1032,6 +1032,9 @@
     <col width="10.75" customWidth="1" style="1" min="21" max="21"/>
     <col width="14.5" customWidth="1" style="1" min="22" max="22"/>
     <col width="11.75" customWidth="1" style="1" min="23" max="23"/>
+    <col width="24" customWidth="1" style="1" min="35" max="35"/>
+    <col width="24" customWidth="1" style="1" min="36" max="36"/>
+    <col width="24" customWidth="1" style="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1205,6 +1208,26 @@
           <t>npc_tags</t>
         </is>
       </c>
+      <c r="AI1" s="0" t="inlineStr">
+        <is>
+          <t>direct_drop_id</t>
+        </is>
+      </c>
+      <c r="AJ1" s="0" t="inlineStr">
+        <is>
+          <t>direct_rune_id</t>
+        </is>
+      </c>
+      <c r="AK1" s="0" t="inlineStr">
+        <is>
+          <t>direct_reward_require_player_kill</t>
+        </is>
+      </c>
+      <c r="AL1" s="0" t="inlineStr">
+        <is>
+          <t>initial_buff_ids</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
@@ -1377,6 +1400,26 @@
           <t>(list#sep=|);string</t>
         </is>
       </c>
+      <c r="AI2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AJ2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AK2" s="0" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="AL2" s="0" t="inlineStr">
+        <is>
+          <t>(list#sep=|),string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
@@ -1545,7 +1588,26 @@
           <t>c,s</t>
         </is>
       </c>
-      <c r="AI3" s="0" t="n"/>
+      <c r="AI3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="AJ3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="AK3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="AL3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="81" customHeight="1" s="1">
       <c r="A4" s="0" t="inlineStr">
@@ -1713,6 +1775,26 @@
           <t>Common NPC content tags for drop pools, recipe pools, and other content matching.</t>
         </is>
       </c>
+      <c r="AI4" s="0" t="inlineStr">
+        <is>
+          <t>死亡时直接结算到玩家背包的掉落包；0表示无</t>
+        </is>
+      </c>
+      <c r="AJ4" s="0" t="inlineStr">
+        <is>
+          <t>死亡时直接授予的Rune；空表示无</t>
+        </is>
+      </c>
+      <c r="AK4" s="0" t="inlineStr">
+        <is>
+          <t>直接死亡奖励是否要求玩家造成致命击杀</t>
+        </is>
+      </c>
+      <c r="AL4" s="0" t="inlineStr">
+        <is>
+          <t>????????? Buff ??</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="0" t="inlineStr">
@@ -1833,6 +1915,14 @@
           <t>orc_common</t>
         </is>
       </c>
+      <c r="AI5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="0" t="n"/>
+      <c r="AK5" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="0" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="0" t="inlineStr">
@@ -1943,6 +2033,13 @@
           <t>orc</t>
         </is>
       </c>
+      <c r="AI6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="0" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="0" t="inlineStr">
@@ -2053,6 +2150,13 @@
           <t>orc</t>
         </is>
       </c>
+      <c r="AI7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="0" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
@@ -2179,6 +2283,13 @@
           <t>human</t>
         </is>
       </c>
+      <c r="AI9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="0" t="n"/>
     </row>
     <row r="10">
       <c r="R10" s="0" t="n"/>
@@ -2283,6 +2394,13 @@
           <t>human</t>
         </is>
       </c>
+      <c r="AI11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="0" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="0" t="inlineStr">
@@ -2393,6 +2511,13 @@
           <t>human</t>
         </is>
       </c>
+      <c r="AI12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="0" t="inlineStr">
@@ -2489,6 +2614,13 @@
         <v>0</v>
       </c>
       <c r="AG13" s="0" t="inlineStr"/>
+      <c r="AI13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="0" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="0" t="inlineStr">
@@ -2594,6 +2726,13 @@
           <t>human</t>
         </is>
       </c>
+      <c r="AI14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="0" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="0" t="inlineStr">
@@ -2699,6 +2838,13 @@
           <t>human</t>
         </is>
       </c>
+      <c r="AI15" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="0" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="0" t="n"/>
@@ -2818,6 +2964,13 @@
           <t>human</t>
         </is>
       </c>
+      <c r="AI17" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="0" t="n"/>
     </row>
     <row r="18">
       <c r="R18" s="0" t="n"/>
@@ -2921,6 +3074,13 @@
         <v>0</v>
       </c>
       <c r="AG19" s="0" t="inlineStr"/>
+      <c r="AI19" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL19" s="0" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="0" t="inlineStr">
@@ -3020,6 +3180,13 @@
         <v>0</v>
       </c>
       <c r="AG20" s="0" t="inlineStr"/>
+      <c r="AI20" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="0" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="0" t="inlineStr">
@@ -3119,6 +3286,13 @@
         <v>0</v>
       </c>
       <c r="AG21" s="0" t="inlineStr"/>
+      <c r="AI21" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL21" s="0" t="n"/>
     </row>
     <row r="22">
       <c r="R22" s="0" t="n"/>
@@ -3222,6 +3396,13 @@
         <v>0</v>
       </c>
       <c r="AG23" s="0" t="inlineStr"/>
+      <c r="AI23" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="0" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="0" t="inlineStr">
@@ -3321,6 +3502,13 @@
         <v>0</v>
       </c>
       <c r="AG24" s="0" t="inlineStr"/>
+      <c r="AI24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="0" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="0" t="inlineStr">
@@ -3420,6 +3608,13 @@
         <v>0</v>
       </c>
       <c r="AG25" s="0" t="inlineStr"/>
+      <c r="AI25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="0" t="n"/>
     </row>
     <row r="26">
       <c r="R26" s="0" t="n"/>
@@ -3523,6 +3718,13 @@
         <v>0</v>
       </c>
       <c r="AG27" s="0" t="inlineStr"/>
+      <c r="AI27" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="0" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="0" t="inlineStr">
@@ -3622,6 +3824,13 @@
         <v>0</v>
       </c>
       <c r="AG28" s="0" t="inlineStr"/>
+      <c r="AI28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="0" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="0" t="inlineStr">
@@ -3721,6 +3930,13 @@
         <v>0</v>
       </c>
       <c r="AG29" s="0" t="inlineStr"/>
+      <c r="AI29" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="0" t="n"/>
     </row>
     <row r="30">
       <c r="R30" s="0" t="n"/>
@@ -3820,6 +4036,13 @@
         <v>0</v>
       </c>
       <c r="AG31" s="0" t="inlineStr"/>
+      <c r="AI31" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="0" t="n"/>
     </row>
     <row r="32">
       <c r="AG32" s="0" t="inlineStr"/>
@@ -3916,6 +4139,13 @@
         <v>0</v>
       </c>
       <c r="AG33" s="0" t="inlineStr"/>
+      <c r="AI33" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="0" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="0" t="inlineStr">
@@ -3984,6 +4214,13 @@
         <v>1</v>
       </c>
       <c r="AG34" s="0" t="inlineStr"/>
+      <c r="AI34" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="0" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="0" t="n"/>
@@ -4113,6 +4350,13 @@
           <t>human</t>
         </is>
       </c>
+      <c r="AI36" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="0" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="0" t="inlineStr">
@@ -4224,6 +4468,13 @@
           <t>human</t>
         </is>
       </c>
+      <c r="AI37" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL37" s="0" t="n"/>
     </row>
     <row r="38" s="1">
       <c r="B38" s="0" t="inlineStr">
@@ -4319,6 +4570,13 @@
       <c r="AF38" s="0" t="b">
         <v>0</v>
       </c>
+      <c r="AI38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL38" s="0" t="n"/>
     </row>
     <row r="39" s="1">
       <c r="B39" s="0" t="inlineStr">
@@ -4434,6 +4692,14 @@
           <t>human</t>
         </is>
       </c>
+      <c r="AI39" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="0" t="n"/>
+      <c r="AK39" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL39" s="0" t="n"/>
     </row>
     <row r="40" s="1">
       <c r="B40" s="0" t="inlineStr">
@@ -4553,6 +4819,14 @@
           <t>human</t>
         </is>
       </c>
+      <c r="AI40" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" s="0" t="n"/>
+      <c r="AK40" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL40" s="0" t="n"/>
     </row>
     <row r="41">
       <c r="B41" s="0" t="inlineStr">
@@ -4671,6 +4945,400 @@
       <c r="AH41" s="0" t="inlineStr">
         <is>
           <t>bandit|human</t>
+        </is>
+      </c>
+      <c r="AI41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="0" t="n"/>
+      <c r="AK41" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL41" s="0" t="n"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>forest_treant_boss</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>深林树妖</t>
+        </is>
+      </c>
+      <c r="D42" s="0" t="inlineStr">
+        <is>
+          <t>盘踞在森林深处的古老树妖。</t>
+        </is>
+      </c>
+      <c r="E42" s="0" t="inlineStr">
+        <is>
+          <t>forest_treant_boss</t>
+        </is>
+      </c>
+      <c r="F42" s="0" t="n">
+        <v>10001</v>
+      </c>
+      <c r="G42" s="0" t="inlineStr">
+        <is>
+          <t>default_monster</t>
+        </is>
+      </c>
+      <c r="H42" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I42" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" s="0" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="K42" s="0" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="L42" s="0" t="inlineStr">
+        <is>
+          <t>default_normal_attack|treant_corrosive_barrage|treant_summon_root_nodes|treant_summon_thorn_vines</t>
+        </is>
+      </c>
+      <c r="M42" s="0" t="n"/>
+      <c r="N42" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O42" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R42" s="0" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="S42" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="0" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W42" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X42" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB42" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="AC42" s="0" t="inlineStr">
+        <is>
+          <t>forest_treant</t>
+        </is>
+      </c>
+      <c r="AD42" s="0" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="AE42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="0" t="inlineStr">
+        <is>
+          <t>monster</t>
+        </is>
+      </c>
+      <c r="AH42" s="0" t="inlineStr">
+        <is>
+          <t>boss|forest</t>
+        </is>
+      </c>
+      <c r="AI42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="0" t="inlineStr">
+        <is>
+          <t>rune_harvest</t>
+        </is>
+      </c>
+      <c r="AK42" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="0" t="n"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t>forest_treant_root_node</t>
+        </is>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>树妖根瘤</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="inlineStr">
+        <is>
+          <t>由树妖召出的固定根瘤。</t>
+        </is>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>forest_treant_root_node</t>
+        </is>
+      </c>
+      <c r="F43" s="0" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G43" s="0" t="inlineStr">
+        <is>
+          <t>default_monster</t>
+        </is>
+      </c>
+      <c r="H43" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="0" t="inlineStr">
+        <is>
+          <t>NoMove</t>
+        </is>
+      </c>
+      <c r="K43" s="0" t="inlineStr">
+        <is>
+          <t>fixed_turret</t>
+        </is>
+      </c>
+      <c r="L43" s="0" t="inlineStr">
+        <is>
+          <t>cannon_shoot_01</t>
+        </is>
+      </c>
+      <c r="M43" s="0" t="n"/>
+      <c r="N43" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="O43" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="0" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="S43" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W43" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X43" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB43" s="0" t="n">
+        <v>360</v>
+      </c>
+      <c r="AC43" s="0" t="inlineStr">
+        <is>
+          <t>forest_treant_summon</t>
+        </is>
+      </c>
+      <c r="AD43" s="0" t="n"/>
+      <c r="AE43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG43" s="0" t="inlineStr">
+        <is>
+          <t>monster</t>
+        </is>
+      </c>
+      <c r="AH43" s="0" t="inlineStr">
+        <is>
+          <t>summon|forest</t>
+        </is>
+      </c>
+      <c r="AI43" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="0" t="n"/>
+      <c r="AK43" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL43" s="0" t="n"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t>forest_treant_thorn_vine</t>
+        </is>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>深林荆棘藤蔓</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="inlineStr">
+        <is>
+          <t>树妖召唤的不可伤害阻挡藤蔓。</t>
+        </is>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>forest_treant_thorn_vine</t>
+        </is>
+      </c>
+      <c r="F44" s="0" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G44" s="0" t="inlineStr">
+        <is>
+          <t>default_monster</t>
+        </is>
+      </c>
+      <c r="H44" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="0" t="inlineStr">
+        <is>
+          <t>NoMove</t>
+        </is>
+      </c>
+      <c r="K44" s="0" t="inlineStr">
+        <is>
+          <t>basic_unit_peace</t>
+        </is>
+      </c>
+      <c r="L44" s="0" t="n"/>
+      <c r="M44" s="0" t="n"/>
+      <c r="N44" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O44" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" s="0" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="S44" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="0" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W44" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X44" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB44" s="0" t="n">
+        <v>180</v>
+      </c>
+      <c r="AC44" s="0" t="inlineStr">
+        <is>
+          <t>forest_treant_vine</t>
+        </is>
+      </c>
+      <c r="AD44" s="0" t="n"/>
+      <c r="AE44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG44" s="0" t="inlineStr">
+        <is>
+          <t>monster</t>
+        </is>
+      </c>
+      <c r="AH44" s="0" t="inlineStr">
+        <is>
+          <t>summon|forest|thorn_vine</t>
+        </is>
+      </c>
+      <c r="AI44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="0" t="n"/>
+      <c r="AK44" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL44" s="0" t="inlineStr">
+        <is>
+          <t>vine_immortal|vine_thorn_contact</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="unit_npc" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,14 +11,14 @@
     <sheet name="desire_density_info" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="3">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -28,344 +28,29 @@
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <family val="3"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -373,254 +58,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -633,57 +76,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="常规 3" xfId="49"/>
+    <cellStyle name="常规 3" xfId="1"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1001,6 +396,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1010,7 +406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL44"/>
+  <dimension ref="A1:AL45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24" customWidth="1" style="1" min="2" max="2"/>
@@ -1032,9 +428,7 @@
     <col width="10.75" customWidth="1" style="1" min="21" max="21"/>
     <col width="14.5" customWidth="1" style="1" min="22" max="22"/>
     <col width="11.75" customWidth="1" style="1" min="23" max="23"/>
-    <col width="24" customWidth="1" style="1" min="35" max="35"/>
-    <col width="24" customWidth="1" style="1" min="36" max="36"/>
-    <col width="24" customWidth="1" style="1" min="37" max="37"/>
+    <col width="24" customWidth="1" style="1" min="35" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1769,7 +1163,6 @@
           <t>lock_initial_face</t>
         </is>
       </c>
-      <c r="AG4" s="0" t="inlineStr"/>
       <c r="AH4" s="0" t="inlineStr">
         <is>
           <t>Common NPC content tags for drop pools, recipe pools, and other content matching.</t>
@@ -1922,7 +1315,6 @@
       <c r="AK5" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL5" s="0" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="0" t="inlineStr">
@@ -2039,7 +1431,6 @@
       <c r="AK6" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL6" s="0" t="n"/>
     </row>
     <row r="7">
       <c r="B7" s="0" t="inlineStr">
@@ -2156,7 +1547,6 @@
       <c r="AK7" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL7" s="0" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
@@ -2180,7 +1570,6 @@
       <c r="AB8" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AG8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="B9" s="0" t="inlineStr">
@@ -2289,11 +1678,9 @@
       <c r="AK9" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL9" s="0" t="n"/>
     </row>
     <row r="10">
       <c r="R10" s="0" t="n"/>
-      <c r="AG10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="B11" s="0" t="inlineStr">
@@ -2400,7 +1787,6 @@
       <c r="AK11" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL11" s="0" t="n"/>
     </row>
     <row r="12">
       <c r="B12" s="0" t="inlineStr">
@@ -2517,7 +1903,6 @@
       <c r="AK12" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL12" s="0" t="n"/>
     </row>
     <row r="13">
       <c r="B13" s="0" t="inlineStr">
@@ -2613,14 +1998,12 @@
       <c r="AF13" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AG13" s="0" t="inlineStr"/>
       <c r="AI13" s="0" t="n">
         <v>0</v>
       </c>
       <c r="AK13" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL13" s="0" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="0" t="inlineStr">
@@ -2732,7 +2115,6 @@
       <c r="AK14" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL14" s="0" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="0" t="inlineStr">
@@ -2844,7 +2226,6 @@
       <c r="AK15" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL15" s="0" t="n"/>
     </row>
     <row r="16">
       <c r="B16" s="0" t="n"/>
@@ -2862,7 +2243,6 @@
       <c r="R16" s="0" t="n"/>
       <c r="V16" s="0" t="n"/>
       <c r="W16" s="0" t="n"/>
-      <c r="AG16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" s="0" t="inlineStr">
@@ -2970,11 +2350,9 @@
       <c r="AK17" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL17" s="0" t="n"/>
     </row>
     <row r="18">
       <c r="R18" s="0" t="n"/>
-      <c r="AG18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" s="0" t="inlineStr">
@@ -3073,14 +2451,12 @@
       <c r="AF19" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AG19" s="0" t="inlineStr"/>
       <c r="AI19" s="0" t="n">
         <v>0</v>
       </c>
       <c r="AK19" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL19" s="0" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="0" t="inlineStr">
@@ -3179,14 +2555,12 @@
       <c r="AF20" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AG20" s="0" t="inlineStr"/>
       <c r="AI20" s="0" t="n">
         <v>0</v>
       </c>
       <c r="AK20" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL20" s="0" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="0" t="inlineStr">
@@ -3285,18 +2659,15 @@
       <c r="AF21" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AG21" s="0" t="inlineStr"/>
       <c r="AI21" s="0" t="n">
         <v>0</v>
       </c>
       <c r="AK21" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL21" s="0" t="n"/>
     </row>
     <row r="22">
       <c r="R22" s="0" t="n"/>
-      <c r="AG22" s="0" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="B23" s="0" t="inlineStr">
@@ -3395,14 +2766,12 @@
       <c r="AF23" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AG23" s="0" t="inlineStr"/>
       <c r="AI23" s="0" t="n">
         <v>0</v>
       </c>
       <c r="AK23" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL23" s="0" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="0" t="inlineStr">
@@ -3501,14 +2870,12 @@
       <c r="AF24" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AG24" s="0" t="inlineStr"/>
       <c r="AI24" s="0" t="n">
         <v>0</v>
       </c>
       <c r="AK24" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL24" s="0" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="0" t="inlineStr">
@@ -3607,18 +2974,15 @@
       <c r="AF25" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AG25" s="0" t="inlineStr"/>
       <c r="AI25" s="0" t="n">
         <v>0</v>
       </c>
       <c r="AK25" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL25" s="0" t="n"/>
     </row>
     <row r="26">
       <c r="R26" s="0" t="n"/>
-      <c r="AG26" s="0" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="B27" s="0" t="inlineStr">
@@ -3717,14 +3081,12 @@
       <c r="AF27" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AG27" s="0" t="inlineStr"/>
       <c r="AI27" s="0" t="n">
         <v>0</v>
       </c>
       <c r="AK27" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL27" s="0" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="0" t="inlineStr">
@@ -3823,14 +3185,12 @@
       <c r="AF28" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AG28" s="0" t="inlineStr"/>
       <c r="AI28" s="0" t="n">
         <v>0</v>
       </c>
       <c r="AK28" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL28" s="0" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="0" t="inlineStr">
@@ -3929,18 +3289,15 @@
       <c r="AF29" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AG29" s="0" t="inlineStr"/>
       <c r="AI29" s="0" t="n">
         <v>0</v>
       </c>
       <c r="AK29" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL29" s="0" t="n"/>
     </row>
     <row r="30">
       <c r="R30" s="0" t="n"/>
-      <c r="AG30" s="0" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="B31" s="0" t="inlineStr">
@@ -4035,18 +3392,14 @@
       <c r="AF31" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AG31" s="0" t="inlineStr"/>
       <c r="AI31" s="0" t="n">
         <v>0</v>
       </c>
       <c r="AK31" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL31" s="0" t="n"/>
-    </row>
-    <row r="32">
-      <c r="AG32" s="0" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="32"/>
     <row r="33">
       <c r="B33" s="0" t="inlineStr">
         <is>
@@ -4138,14 +3491,12 @@
       <c r="AF33" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AG33" s="0" t="inlineStr"/>
       <c r="AI33" s="0" t="n">
         <v>0</v>
       </c>
       <c r="AK33" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL33" s="0" t="n"/>
     </row>
     <row r="34">
       <c r="B34" s="0" t="inlineStr">
@@ -4213,14 +3564,12 @@
       <c r="AF34" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="AG34" s="0" t="inlineStr"/>
       <c r="AI34" s="0" t="n">
         <v>0</v>
       </c>
       <c r="AK34" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL34" s="0" t="n"/>
     </row>
     <row r="35">
       <c r="B35" s="0" t="n"/>
@@ -4238,7 +3587,6 @@
       <c r="O35" s="0" t="n"/>
       <c r="Q35" s="0" t="n"/>
       <c r="R35" s="0" t="n"/>
-      <c r="AG35" s="0" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="B36" s="0" t="inlineStr">
@@ -4356,7 +3704,6 @@
       <c r="AK36" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL36" s="0" t="n"/>
     </row>
     <row r="37">
       <c r="B37" s="0" t="inlineStr">
@@ -4474,9 +3821,8 @@
       <c r="AK37" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL37" s="0" t="n"/>
-    </row>
-    <row r="38" s="1">
+    </row>
+    <row r="38">
       <c r="B38" s="0" t="inlineStr">
         <is>
           <t>forest_fly_swarm</t>
@@ -4576,9 +3922,8 @@
       <c r="AK38" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL38" s="0" t="n"/>
-    </row>
-    <row r="39" s="1">
+    </row>
+    <row r="39">
       <c r="B39" s="0" t="inlineStr">
         <is>
           <t>game_init_carlisle_unconscious</t>
@@ -4602,7 +3947,7 @@
       <c r="F39" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="0" t="inlineStr"/>
+      <c r="G39" s="0" t="n"/>
       <c r="H39" s="0" t="n">
         <v>0</v>
       </c>
@@ -4619,8 +3964,8 @@
           <t>default</t>
         </is>
       </c>
-      <c r="L39" s="0" t="inlineStr"/>
-      <c r="M39" s="0" t="inlineStr"/>
+      <c r="L39" s="0" t="n"/>
+      <c r="M39" s="0" t="n"/>
       <c r="N39" s="0" t="b">
         <v>1</v>
       </c>
@@ -4670,7 +4015,6 @@
       <c r="AB39" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AC39" s="0" t="inlineStr"/>
       <c r="AD39" s="0" t="inlineStr">
         <is>
           <t>human</t>
@@ -4699,9 +4043,8 @@
       <c r="AK39" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL39" s="0" t="n"/>
-    </row>
-    <row r="40" s="1">
+    </row>
+    <row r="40">
       <c r="B40" s="0" t="inlineStr">
         <is>
           <t>game_init_carlisle_awake</t>
@@ -4746,8 +4089,8 @@
           <t>default</t>
         </is>
       </c>
-      <c r="L40" s="0" t="inlineStr"/>
-      <c r="M40" s="0" t="inlineStr"/>
+      <c r="L40" s="0" t="n"/>
+      <c r="M40" s="0" t="n"/>
       <c r="N40" s="0" t="b">
         <v>1</v>
       </c>
@@ -4797,7 +4140,6 @@
       <c r="AB40" s="0" t="n">
         <v>-1</v>
       </c>
-      <c r="AC40" s="0" t="inlineStr"/>
       <c r="AD40" s="0" t="inlineStr">
         <is>
           <t>human</t>
@@ -4826,7 +4168,6 @@
       <c r="AK40" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL40" s="0" t="n"/>
     </row>
     <row r="41">
       <c r="B41" s="0" t="inlineStr">
@@ -4954,7 +4295,6 @@
       <c r="AK41" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL41" s="0" t="n"/>
     </row>
     <row r="42">
       <c r="B42" s="0" t="inlineStr">
@@ -5088,7 +4428,6 @@
       <c r="AK42" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL42" s="0" t="n"/>
     </row>
     <row r="43">
       <c r="B43" s="0" t="inlineStr">
@@ -5190,7 +4529,6 @@
           <t>forest_treant_summon</t>
         </is>
       </c>
-      <c r="AD43" s="0" t="n"/>
       <c r="AE43" s="0" t="n">
         <v>0</v>
       </c>
@@ -5214,7 +4552,6 @@
       <c r="AK43" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="AL43" s="0" t="n"/>
     </row>
     <row r="44">
       <c r="B44" s="0" t="inlineStr">
@@ -5312,7 +4649,6 @@
           <t>forest_treant_vine</t>
         </is>
       </c>
-      <c r="AD44" s="0" t="n"/>
       <c r="AE44" s="0" t="n">
         <v>0</v>
       </c>
@@ -5340,6 +4676,123 @@
         <is>
           <t>vine_immortal|vine_thorn_contact</t>
         </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t>home_vera</t>
+        </is>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>薇拉</t>
+        </is>
+      </c>
+      <c r="D45" s="0" t="inlineStr">
+        <is>
+          <t>CharacterKey=home_vera; former exiled attendant; non-combat support NPC</t>
+        </is>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>vera_civil</t>
+        </is>
+      </c>
+      <c r="F45" s="0" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G45" s="0" t="inlineStr">
+        <is>
+          <t>default_peace</t>
+        </is>
+      </c>
+      <c r="H45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="0" t="inlineStr">
+        <is>
+          <t>NoMove</t>
+        </is>
+      </c>
+      <c r="K45" s="0" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="N45" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O45" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P45" s="0" t="inlineStr">
+        <is>
+          <t>npc_generic_entry</t>
+        </is>
+      </c>
+      <c r="Q45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="0" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="S45" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="U45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W45" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X45" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB45" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD45" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AE45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AI45" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" s="0" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5986,7 +5439,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="15.625" customWidth="1" style="1" min="2" max="2"/>
     <col width="12.25" customWidth="1" style="1" min="3" max="3"/>

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="unit_npc" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="unit_npc_attribute" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="desire_density_info" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_npc" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_npc_attribute" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="desire_density_info" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -406,7 +406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL45"/>
+  <dimension ref="A1:AL47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24" customWidth="1" style="1" min="2" max="2"/>
@@ -4795,6 +4795,112 @@
         <v>0</v>
       </c>
     </row>
+    <row r="46">
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t>home_evan</t>
+        </is>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>艾文</t>
+        </is>
+      </c>
+      <c r="D46" s="0" t="inlineStr">
+        <is>
+          <t>Home 01 named NPC</t>
+        </is>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>civil</t>
+        </is>
+      </c>
+      <c r="F46" s="0" t="n"/>
+      <c r="G46" s="0" t="n"/>
+      <c r="H46" s="0" t="n"/>
+      <c r="I46" s="0" t="n"/>
+      <c r="J46" s="0" t="n"/>
+      <c r="K46" s="0" t="n"/>
+      <c r="N46" s="0" t="n"/>
+      <c r="O46" s="0" t="n"/>
+      <c r="P46" s="0" t="inlineStr">
+        <is>
+          <t>npc_generic_entry</t>
+        </is>
+      </c>
+      <c r="Q46" s="0" t="n"/>
+      <c r="R46" s="0" t="n"/>
+      <c r="S46" s="0" t="n"/>
+      <c r="T46" s="0" t="n"/>
+      <c r="U46" s="0" t="n"/>
+      <c r="V46" s="0" t="n"/>
+      <c r="W46" s="0" t="n"/>
+      <c r="X46" s="0" t="n"/>
+      <c r="Y46" s="0" t="n"/>
+      <c r="Z46" s="0" t="n"/>
+      <c r="AA46" s="0" t="n"/>
+      <c r="AB46" s="0" t="n"/>
+      <c r="AD46" s="0" t="n"/>
+      <c r="AE46" s="0" t="n"/>
+      <c r="AF46" s="0" t="n"/>
+      <c r="AG46" s="0" t="n"/>
+      <c r="AI46" s="0" t="n"/>
+      <c r="AK46" s="0" t="n"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="0" t="inlineStr">
+        <is>
+          <t>home_hearn</t>
+        </is>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t>赫恩</t>
+        </is>
+      </c>
+      <c r="D47" s="0" t="inlineStr">
+        <is>
+          <t>Home 01 named NPC</t>
+        </is>
+      </c>
+      <c r="E47" s="0" t="inlineStr">
+        <is>
+          <t>civil</t>
+        </is>
+      </c>
+      <c r="F47" s="0" t="n"/>
+      <c r="G47" s="0" t="n"/>
+      <c r="H47" s="0" t="n"/>
+      <c r="I47" s="0" t="n"/>
+      <c r="J47" s="0" t="n"/>
+      <c r="K47" s="0" t="n"/>
+      <c r="N47" s="0" t="n"/>
+      <c r="O47" s="0" t="n"/>
+      <c r="P47" s="0" t="inlineStr">
+        <is>
+          <t>npc_generic_entry</t>
+        </is>
+      </c>
+      <c r="Q47" s="0" t="n"/>
+      <c r="R47" s="0" t="n"/>
+      <c r="S47" s="0" t="n"/>
+      <c r="T47" s="0" t="n"/>
+      <c r="U47" s="0" t="n"/>
+      <c r="V47" s="0" t="n"/>
+      <c r="W47" s="0" t="n"/>
+      <c r="X47" s="0" t="n"/>
+      <c r="Y47" s="0" t="n"/>
+      <c r="Z47" s="0" t="n"/>
+      <c r="AA47" s="0" t="n"/>
+      <c r="AB47" s="0" t="n"/>
+      <c r="AD47" s="0" t="n"/>
+      <c r="AE47" s="0" t="n"/>
+      <c r="AF47" s="0" t="n"/>
+      <c r="AG47" s="0" t="n"/>
+      <c r="AI47" s="0" t="n"/>
+      <c r="AK47" s="0" t="n"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_npc" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_npc_attribute" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="desire_density_info" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="unit_npc" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="unit_npc_attribute" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="desire_density_info" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -406,7 +406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL47"/>
+  <dimension ref="A1:AL51"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="24" customWidth="1" style="1" min="2" max="2"/>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="F14" s="0" t="n">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
@@ -4901,6 +4901,470 @@
       <c r="AI47" s="0" t="n"/>
       <c r="AK47" s="0" t="n"/>
     </row>
+    <row r="48">
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>civil_apprentice</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>学徒</t>
+        </is>
+      </c>
+      <c r="D48" s="0" t="inlineStr">
+        <is>
+          <t>年轻的城镇学徒</t>
+        </is>
+      </c>
+      <c r="E48" s="0" t="inlineStr">
+        <is>
+          <t>civil</t>
+        </is>
+      </c>
+      <c r="F48" s="0" t="n">
+        <v>12001</v>
+      </c>
+      <c r="G48" s="0" t="inlineStr">
+        <is>
+          <t>default_npc</t>
+        </is>
+      </c>
+      <c r="H48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" s="0" t="inlineStr">
+        <is>
+          <t>NoMove</t>
+        </is>
+      </c>
+      <c r="K48" s="0" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="M48" s="0" t="inlineStr">
+        <is>
+          <t>default_h_attack|default_enemy_harass|default_enemy_knockdown_push</t>
+        </is>
+      </c>
+      <c r="N48" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O48" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P48" s="0" t="inlineStr">
+        <is>
+          <t>qigai_01</t>
+        </is>
+      </c>
+      <c r="Q48" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R48" s="0" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="S48" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V48" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W48" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X48" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB48" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD48" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AE48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AI48" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t>civil_woman</t>
+        </is>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t>妇人</t>
+        </is>
+      </c>
+      <c r="D49" s="0" t="inlineStr">
+        <is>
+          <t>城镇居民</t>
+        </is>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>civil</t>
+        </is>
+      </c>
+      <c r="F49" s="0" t="n">
+        <v>12002</v>
+      </c>
+      <c r="G49" s="0" t="inlineStr">
+        <is>
+          <t>default_npc</t>
+        </is>
+      </c>
+      <c r="H49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="0" t="inlineStr">
+        <is>
+          <t>NoMove</t>
+        </is>
+      </c>
+      <c r="K49" s="0" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="M49" s="0" t="inlineStr">
+        <is>
+          <t>default_h_attack|default_enemy_harass|default_enemy_knockdown_push</t>
+        </is>
+      </c>
+      <c r="N49" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O49" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P49" s="0" t="inlineStr">
+        <is>
+          <t>qigai_01</t>
+        </is>
+      </c>
+      <c r="Q49" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R49" s="0" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="S49" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V49" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W49" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X49" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB49" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD49" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AE49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AI49" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t>civil_elder</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>老者</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="inlineStr">
+        <is>
+          <t>年长的城镇居民</t>
+        </is>
+      </c>
+      <c r="E50" s="0" t="inlineStr">
+        <is>
+          <t>civil</t>
+        </is>
+      </c>
+      <c r="F50" s="0" t="n">
+        <v>12003</v>
+      </c>
+      <c r="G50" s="0" t="inlineStr">
+        <is>
+          <t>default_npc</t>
+        </is>
+      </c>
+      <c r="H50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" s="0" t="inlineStr">
+        <is>
+          <t>NoMove</t>
+        </is>
+      </c>
+      <c r="K50" s="0" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="M50" s="0" t="inlineStr">
+        <is>
+          <t>default_h_attack|default_enemy_harass|default_enemy_knockdown_push</t>
+        </is>
+      </c>
+      <c r="N50" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O50" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P50" s="0" t="inlineStr">
+        <is>
+          <t>qigai_01</t>
+        </is>
+      </c>
+      <c r="Q50" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R50" s="0" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="S50" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V50" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W50" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X50" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB50" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD50" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AE50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AI50" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t>civil_worker</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>工匠</t>
+        </is>
+      </c>
+      <c r="D51" s="0" t="inlineStr">
+        <is>
+          <t>负责维修与生产的城镇工匠</t>
+        </is>
+      </c>
+      <c r="E51" s="0" t="inlineStr">
+        <is>
+          <t>civil</t>
+        </is>
+      </c>
+      <c r="F51" s="0" t="n">
+        <v>12004</v>
+      </c>
+      <c r="G51" s="0" t="inlineStr">
+        <is>
+          <t>default_npc</t>
+        </is>
+      </c>
+      <c r="H51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="0" t="inlineStr">
+        <is>
+          <t>NoMove</t>
+        </is>
+      </c>
+      <c r="K51" s="0" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="M51" s="0" t="inlineStr">
+        <is>
+          <t>default_h_attack|default_enemy_harass|default_enemy_knockdown_push</t>
+        </is>
+      </c>
+      <c r="N51" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="O51" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="P51" s="0" t="inlineStr">
+        <is>
+          <t>qigai_01</t>
+        </is>
+      </c>
+      <c r="Q51" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="R51" s="0" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="S51" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="V51" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W51" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="X51" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AB51" s="0" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD51" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AE51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="0" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="AI51" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="0" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -4913,7 +5377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="18.75" customWidth="1" style="1" min="2" max="3"/>
@@ -5530,6 +5994,136 @@
       </c>
       <c r="K22" s="0" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="0" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>70</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="I23" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="0" t="n">
+        <v>12001</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="0" t="n">
+        <v>65</v>
+      </c>
+      <c r="E24" s="0" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F24" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="0" t="n">
+        <v>12002</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>75</v>
+      </c>
+      <c r="E25" s="0" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="F25" s="0" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G25" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="0" t="n">
+        <v>12003</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="0" t="n">
+        <v>55</v>
+      </c>
+      <c r="E26" s="0" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F26" s="0" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G26" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="0" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="0" t="n">
+        <v>12004</v>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>95</v>
+      </c>
+      <c r="E27" s="0" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F27" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="I27" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" s="0" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -2018,7 +2018,7 @@
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t>civil</t>
+          <t>civil_shell</t>
         </is>
       </c>
       <c r="F14" s="0" t="n">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
-          <t>civil</t>
+          <t>civil_shell</t>
         </is>
       </c>
       <c r="F48" s="0" t="n">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
-          <t>civil</t>
+          <t>civil_shell</t>
         </is>
       </c>
       <c r="F49" s="0" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
-          <t>civil</t>
+          <t>civil_shell</t>
         </is>
       </c>
       <c r="F50" s="0" t="n">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
-          <t>civil</t>
+          <t>civil_shell</t>
         </is>
       </c>
       <c r="F51" s="0" t="n">

--- a/Config/Datas/unit_npc.xlsx
+++ b/Config/Datas/unit_npc.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_npc" sheetId="1" r:id="R69bb2c9959d94c84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_npc_attribute" sheetId="2" r:id="R577a1ede65d3436f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="desire_density_info" sheetId="3" r:id="R6346d422f9684407"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_npc" sheetId="1" r:id="Rcfc8bfaf7ee140ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unit_npc_attribute" sheetId="2" r:id="R81c40c1bfc8e4f56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="desire_density_info" sheetId="3" r:id="R7a753189f67b41de"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5469,27 +5469,106 @@
       <x:c r="AL45"/>
     </x:row>
     <x:row r="46">
-      <x:c r="B46"/>
-      <x:c r="C46"/>
-      <x:c r="D46"/>
-      <x:c r="E46"/>
-      <x:c r="F46"/>
-      <x:c r="G46"/>
-      <x:c r="H46"/>
-      <x:c r="I46"/>
-      <x:c r="J46"/>
-      <x:c r="K46"/>
-      <x:c r="N46"/>
-      <x:c r="O46"/>
+      <x:c r="A46"/>
+      <x:c r="B46" t="str">
+        <x:v>magic_orb_basic</x:v>
+      </x:c>
+      <x:c r="C46" t="str">
+        <x:v>魔能弹</x:v>
+      </x:c>
+      <x:c r="D46" t="str">
+        <x:v>由技能制造、短暂存在并在读条结束后自毁的魔能弹。</x:v>
+      </x:c>
+      <x:c r="E46" t="str">
+        <x:v>magic_orb_basic</x:v>
+      </x:c>
+      <x:c r="F46" t="n">
+        <x:v>10021</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>default_npc</x:v>
+      </x:c>
+      <x:c r="H46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>NoMove</x:v>
+      </x:c>
+      <x:c r="K46" t="str">
+        <x:v>self_locked_combat</x:v>
+      </x:c>
+      <x:c r="L46" t="str">
+        <x:v>magic_orb_shell_passive|magic_orb_self_destruct</x:v>
+      </x:c>
+      <x:c r="M46"/>
+      <x:c r="N46" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="O46" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="P46"/>
-      <x:c r="Q46"/>
-      <x:c r="R46"/>
-      <x:c r="T46"/>
-      <x:c r="U46"/>
-      <x:c r="V46"/>
-      <x:c r="W46"/>
-      <x:c r="AI46"/>
-      <x:c r="AK46"/>
+      <x:c r="Q46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="R46" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="S46" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T46" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V46" t="n">
+        <x:v>0.35</x:v>
+      </x:c>
+      <x:c r="W46" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X46" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y46" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="Z46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AA46" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="AB46" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="AC46" t="str">
+        <x:v>magic_orb</x:v>
+      </x:c>
+      <x:c r="AD46"/>
+      <x:c r="AE46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AF46" s="3" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AG46"/>
+      <x:c r="AH46" t="str">
+        <x:v>summon|magic_orb</x:v>
+      </x:c>
+      <x:c r="AI46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AJ46"/>
+      <x:c r="AK46" s="3" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AL46"/>
     </x:row>
     <x:row r="47">
       <x:c r="B47"/>
@@ -6637,15 +6716,40 @@
       </x:c>
     </x:row>
     <x:row r="27">
-      <x:c r="B27"/>
-      <x:c r="C27"/>
-      <x:c r="D27"/>
-      <x:c r="E27"/>
-      <x:c r="F27"/>
-      <x:c r="G27"/>
-      <x:c r="I27"/>
-      <x:c r="J27"/>
-      <x:c r="K27"/>
+      <x:c r="A27"/>
+      <x:c r="B27" t="n">
+        <x:v>10021</x:v>
+      </x:c>
+      <x:c r="C27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D27" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L27" t="n">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="B28"/>
